--- a/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
+++ b/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -592,17 +592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.263,00</t>
+          <t>R$ 2.818,00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>▼ 34,3%</t>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>770</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,3%</t>
+        <v>918</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,24 +744,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.969,00</t>
+          <t>R$ 3.338,00</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,9%</t>
+          <t>▼ 15,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>979</v>
+        <v>903</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,6%</t>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.637,00</t>
+          <t>R$ 3.931,00</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>▲ 68,9%</t>
+          <t>▲ 20,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>973</v>
+        <v>817</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,1%</t>
+          <t>▲ 6,1%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1030,17 +1030,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
+          <t>R$ 3.263,00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,1%</t>
+          <t>▼ 34,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>810</v>
+        <v>770</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,4%</t>
+          <t>▼ 21,3%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1182,24 +1182,24 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.592,00</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,5%</t>
+          <t>R$ 4.969,00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>914</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,5%</t>
+        <v>979</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,6%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1328,11 +1328,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.472,00</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,3%</t>
+          <t>R$ 5.637,00</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 68,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1057</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 1,7%</t>
+        <v>973</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,1%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1474,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.629,00</t>
+          <t>R$ 3.338,00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,6%</t>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1075</v>
+        <v>810</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,7%</t>
+          <t>▼ 11,4%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1620,11 +1620,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.747,00</t>
+          <t>R$ 3.592,00</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>▲ 68,5%</t>
+          <t>▲ 3,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1116</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,7%</t>
+        <v>914</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,5%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1760,17 +1760,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
+          <t>R$ 3.472,00</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>▼ 45,7%</t>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>973</v>
+        <v>1057</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▼ 35,1%</t>
+          <t>▼ 1,7%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1912,24 +1912,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.186,00</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 45,7%</t>
+          <t>R$ 3.629,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27,9%</t>
+        <v>1075</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,7%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2058,11 +2058,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.560,00</t>
+          <t>R$ 4.747,00</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,3%</t>
+          <t>▲ 68,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1173</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,4%</t>
+        <v>1116</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,7%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2198,9 +2198,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.412,00</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,9%</t>
+          <t>R$ 2.818,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 45,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,4%</t>
+        <v>973</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,1%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2363,11 +2363,11 @@
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 54,1%</t>
+          <t>R$ 5.186,00</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 45,7%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1165</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 47,2%</t>
+        <v>1500</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27,9%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2496,11 +2496,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.304,00</t>
+          <t>R$ 3.560,00</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>▲ 117,9%</t>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>2206</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 101,1%</t>
+        <v>1173</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,4%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2642,11 +2642,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
+          <t>R$ 3.412,00</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>▲ 34,7%</t>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1097</v>
+        <v>1240</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,0%</t>
+          <t>▲ 6,4%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2788,11 +2788,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.147,00</t>
+          <t>R$ 2.893,00</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▼ 54,1%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>930</v>
+        <v>1165</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,1%</t>
+          <t>▼ 47,2%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2934,11 +2934,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.823,00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,6%</t>
+          <t>R$ 6.304,00</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 117,9%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1070</v>
+        <v>2206</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,8%</t>
+          <t>▲ 101,1%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3080,11 +3080,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,38 +3144,38 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.469,00</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,4%</t>
+          <t>R$ 2.893,00</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1061</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,4%</t>
+        <v>1097</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.708,00</t>
+          <t>R$ 2.147,00</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>▼ 0,9%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1368</v>
+        <v>930</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,9%</t>
+          <t>▼ 13,1%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3374,9 +3374,9 @@
       <c r="I40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,20 +3436,20 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.742,00</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,5%</t>
+          <t>R$ 2.823,00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1485</v>
+        <v>1070</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,6%</t>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3458,11 +3458,11 @@
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3518,11 +3518,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,25 +3582,25 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.241,00</t>
+          <t>R$ 3.469,00</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,1%</t>
+          <t>▼ 6,4%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1211</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,2%</t>
+        <v>1061</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,4%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3664,11 +3664,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.072,00</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,1%</t>
+          <t>R$ 3.708,00</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,9%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1208</v>
+        <v>1368</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>▼ 0,2%</t>
+          <t>▼ 7,9%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3810,11 +3810,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,33 +3874,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.650,00</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,4%</t>
+          <t>R$ 3.742,00</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,5%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1211</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,6%</t>
+        <v>1485</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3956,11 +3956,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4020,33 +4020,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.918,00</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,4%</t>
+          <t>R$ 3.241,00</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,1%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1402</v>
+        <v>1211</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,3%</t>
+          <t>▲ 0,2%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4102,11 +4102,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.720,00</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,4%</t>
+          <t>R$ 5.072,00</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,1%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1398</v>
+        <v>1208</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,3%</t>
+          <t>▼ 0,2%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4250,9 +4250,9 @@
       <c r="I52" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4312,33 +4312,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.246,00</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+          <t>R$ 4.650,00</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1541</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,9%</t>
+        <v>1211</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4394,11 +4394,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4458,33 +4458,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.677,00</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,0%</t>
+          <t>R$ 5.918,00</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,4%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1244</v>
+        <v>1402</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,2%</t>
+          <t>▲ 0,3%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4540,11 +4540,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4604,38 +4604,38 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.523,00</t>
+          <t>R$ 4.720,00</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>▼ 19,3%</t>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1205</v>
+        <v>1398</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,3%</t>
+          <t>▼ 9,3%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4680,17 +4680,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,33 +4750,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.368,00</t>
+          <t>R$ 6.246,00</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>▲ 21,6%</t>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1344</v>
+        <v>1541</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,9%</t>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4832,24 +4832,24 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4896,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.593,00</t>
+          <t>R$ 2.677,00</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 24,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1319</v>
+        <v>1244</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,8%</t>
+          <t>▲ 3,2%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4978,11 +4978,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5042,38 +5042,38 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.791,00</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 30,8%</t>
+          <t>R$ 3.523,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 19,3%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1308</v>
+        <v>1205</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▼ 1,4%</t>
+          <t>▼ 10,3%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5118,17 +5118,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5188,38 +5188,38 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.663,00</t>
+          <t>R$ 4.368,00</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,8%</t>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1326</v>
+        <v>1344</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,3%</t>
+          <t>▲ 1,9%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5270,24 +5270,24 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5334,38 +5334,38 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.959,00</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 3.593,00</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1181</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>1319</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5480,33 +5480,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.959,00</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+          <t>R$ 4.791,00</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1268</v>
+        <v>1308</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,2%</t>
+          <t>▼ 1,4%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5626,20 +5626,20 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.988,00</t>
+          <t>R$ 3.663,00</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>▲ 94,0%</t>
+          <t>▲ 23,8%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>2156</v>
+        <v>1326</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>▲ 105,9%</t>
+          <t>▲ 12,3%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5648,16 +5648,16 @@
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5708,11 +5708,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5772,38 +5772,38 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.086,00</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,6%</t>
+          <t>R$ 2.959,00</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1047</v>
+        <v>1181</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,7%</t>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5854,11 +5854,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5918,33 +5918,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.170,00</t>
+          <t>R$ 2.959,00</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1099</v>
+        <v>1268</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,9%</t>
+          <t>▼ 41,2%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6000,11 +6000,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6034,78 +6034,516 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 5.988,00</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 94,0%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>2156</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 105,9%</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>56,8%</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.086,00</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>1047</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,7%</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>40,2%</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.170,00</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>UTD-092</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo Inox</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>3284176106</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>R$ 4.227,00</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
+      <c r="I83" s="2" t="n">
         <v>1247</v>
       </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="J83" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="K83" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="L77" s="2" t="n">
+      <c r="L83" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="M77" s="2" t="inlineStr">
+      <c r="M83" s="2" t="inlineStr">
         <is>
           <t>45,9%</t>
         </is>
       </c>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
+++ b/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+          <t>R$ 3.857,00</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,7%</t>
+        <v>896</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,4%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -746,9 +746,9 @@
       <c r="I4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
+          <t>R$ 2.818,00</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,1%</t>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>903</v>
+        <v>918</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,5%</t>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,5%</t>
+          <t>R$ 3.338,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>817</v>
+        <v>903</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,1%</t>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1030,17 +1030,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.263,00</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 34,3%</t>
+          <t>R$ 3.931,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>770</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,3%</t>
+        <v>817</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,1%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.969,00</t>
+          <t>R$ 3.263,00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,9%</t>
+          <t>▼ 34,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>979</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,6%</t>
+        <v>770</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,3%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1328,24 +1328,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.637,00</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 68,9%</t>
+          <t>R$ 4.969,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,1%</t>
+          <t>▲ 0,6%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1474,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+          <t>R$ 5.637,00</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 68,9%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>810</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,4%</t>
+        <v>973</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,1%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1620,11 +1620,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1684,25 +1684,25 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.592,00</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,5%</t>
+          <t>R$ 3.338,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>914</v>
+        <v>810</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,5%</t>
+          <t>▼ 11,4%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1766,11 +1766,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.472,00</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,3%</t>
+          <t>R$ 3.592,00</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1057</v>
+        <v>914</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▼ 1,7%</t>
+          <t>▼ 13,5%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1912,11 +1912,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.629,00</t>
+          <t>R$ 3.472,00</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,6%</t>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1075</v>
+        <v>1057</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,7%</t>
+          <t>▼ 1,7%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.747,00</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 68,5%</t>
+          <t>R$ 3.629,00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1116</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,7%</t>
+        <v>1075</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,7%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2198,17 +2198,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 45,7%</t>
+          <t>R$ 4.747,00</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 68,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>973</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,1%</t>
+        <v>1116</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,7%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.186,00</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 45,7%</t>
+          <t>R$ 2.818,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 45,7%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27,9%</t>
+        <v>973</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,1%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2496,11 +2496,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2509,11 +2509,11 @@
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.560,00</t>
+          <t>R$ 5.186,00</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,3%</t>
+          <t>▲ 45,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1173</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,4%</t>
+        <v>1500</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27,9%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2642,11 +2642,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.412,00</t>
+          <t>R$ 3.560,00</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>▲ 17,9%</t>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,4%</t>
+        <v>1173</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,4%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2788,11 +2788,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 54,1%</t>
+          <t>R$ 3.412,00</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1165</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 47,2%</t>
+        <v>1240</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,4%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2934,11 +2934,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.304,00</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 117,9%</t>
+          <t>R$ 2.893,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 54,1%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>2206</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 101,1%</t>
+        <v>1165</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,2%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3080,11 +3080,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
+          <t>R$ 6.304,00</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>▲ 34,7%</t>
+          <t>▲ 117,9%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1097</v>
+        <v>2206</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,0%</t>
+          <t>▲ 101,1%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.147,00</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,9%</t>
+          <t>R$ 2.893,00</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>930</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,1%</t>
+        <v>1097</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3372,11 +3372,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.823,00</t>
+          <t>R$ 2.147,00</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,6%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1070</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,8%</t>
+        <v>930</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,1%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3518,11 +3518,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3582,38 +3582,38 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.469,00</t>
+          <t>R$ 2.823,00</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,4%</t>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1061</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,4%</t>
+        <v>1070</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -3625,14 +3625,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3664,11 +3664,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,14 +3698,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3728,38 +3728,38 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.708,00</t>
+          <t>R$ 3.469,00</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>▼ 0,9%</t>
+          <t>▼ 6,4%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1368</v>
+        <v>1061</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,9%</t>
+          <t>▼ 22,4%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3771,14 +3771,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3844,14 +3844,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3874,33 +3874,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.742,00</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,5%</t>
+          <t>R$ 3.708,00</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,9%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1485</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,6%</t>
+        <v>1368</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,9%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3990,14 +3990,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4020,33 +4020,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.241,00</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,1%</t>
+          <t>R$ 3.742,00</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,5%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1211</v>
+        <v>1485</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,2%</t>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4104,9 +4104,9 @@
       <c r="I50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,14 +4136,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4166,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.072,00</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,1%</t>
+          <t>R$ 3.241,00</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,1%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1208</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 0,2%</t>
+        <v>1211</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,2%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,14 +4209,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4248,11 +4248,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4282,14 +4282,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4312,33 +4312,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.650,00</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,4%</t>
+          <t>R$ 5.072,00</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,1%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,6%</t>
+          <t>▼ 0,2%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,14 +4355,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4394,11 +4394,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,14 +4428,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4458,33 +4458,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.918,00</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,4%</t>
+          <t>R$ 4.650,00</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1402</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,3%</t>
+        <v>1211</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,14 +4501,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4540,11 +4540,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4574,14 +4574,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4604,33 +4604,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.720,00</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,4%</t>
+          <t>R$ 5.918,00</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,4%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1398</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,3%</t>
+        <v>1402</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,3%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,14 +4647,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4686,11 +4686,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4720,14 +4720,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4750,33 +4750,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.246,00</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+          <t>R$ 4.720,00</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1541</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,9%</t>
+        <v>1398</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,3%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,14 +4793,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4832,11 +4832,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4866,14 +4866,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4896,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.677,00</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,0%</t>
+          <t>R$ 6.246,00</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1244</v>
+        <v>1541</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,2%</t>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,14 +4939,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4978,11 +4978,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5012,14 +5012,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5042,38 +5042,38 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.523,00</t>
+          <t>R$ 2.677,00</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>▼ 19,3%</t>
+          <t>▼ 24,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1205</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,3%</t>
+        <v>1244</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,2%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5085,14 +5085,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5118,17 +5118,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5158,14 +5158,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5188,38 +5188,38 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.368,00</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,6%</t>
+          <t>R$ 3.523,00</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 19,3%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1344</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,9%</t>
+        <v>1205</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,3%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5231,14 +5231,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5261,33 +5261,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5304,14 +5304,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5334,33 +5334,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.593,00</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+          <t>R$ 4.368,00</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1319</v>
+        <v>1344</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,8%</t>
+          <t>▲ 1,9%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,14 +5377,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5416,24 +5416,24 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5450,14 +5450,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5480,33 +5480,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.791,00</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 30,8%</t>
+          <t>R$ 3.593,00</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1308</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 1,4%</t>
+        <v>1319</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,14 +5523,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5562,11 +5562,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5596,14 +5596,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5626,38 +5626,38 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.663,00</t>
+          <t>R$ 4.791,00</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,8%</t>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1326</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,3%</t>
+        <v>1308</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 1,4%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5669,14 +5669,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5708,11 +5708,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5742,14 +5742,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5772,33 +5772,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.959,00</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 3.663,00</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,8%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1181</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>1326</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,3%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,14 +5815,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5854,11 +5854,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5888,14 +5888,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5921,35 +5921,35 @@
           <t>R$ 2.959,00</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1268</v>
+        <v>1181</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,2%</t>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
@@ -5961,14 +5961,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6000,11 +6000,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6034,14 +6034,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6064,33 +6064,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.988,00</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 94,0%</t>
+          <t>R$ 2.959,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>2156</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 105,9%</t>
+        <v>1268</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,2%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6148,9 +6148,9 @@
       <c r="I78" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6180,14 +6180,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6210,33 +6210,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.086,00</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,6%</t>
+          <t>R$ 5.988,00</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 94,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1047</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,7%</t>
+        <v>2156</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 105,9%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6253,14 +6253,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6292,11 +6292,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6326,14 +6326,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6356,20 +6356,20 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.170,00</t>
+          <t>R$ 3.086,00</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1099</v>
+        <v>1047</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,9%</t>
+          <t>▼ 4,7%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6378,11 +6378,11 @@
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6399,14 +6399,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6438,11 +6438,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6472,78 +6472,224 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.170,00</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>UTD-092</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo Inox</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>3284176106</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>R$ 4.227,00</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
+      <c r="I85" s="2" t="n">
         <v>1247</v>
       </c>
-      <c r="J83" s="2" t="inlineStr">
+      <c r="J85" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K83" s="2" t="inlineStr">
+      <c r="K85" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="L83" s="2" t="n">
+      <c r="L85" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="M83" s="2" t="inlineStr">
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>45,9%</t>
         </is>
       </c>
-      <c r="N83" s="2" t="inlineStr">
+      <c r="N85" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
+++ b/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,25 +662,25 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 36,9%</t>
+          <t>R$ 3.931,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 26,2%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>896</v>
+        <v>848</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,4%</t>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,17 +738,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+          <t>R$ 3.115,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>918</v>
+        <v>834</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,7%</t>
+          <t>▼ 14,5%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -890,24 +890,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,5%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
+          <t>R$ 4.895,00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,1%</t>
+          <t>▲ 26,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>903</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,5%</t>
+        <v>976</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▲ 8,9%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▲ 166,7%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,5%</t>
+          <t>R$ 3.857,00</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>817</v>
+        <v>896</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,1%</t>
+          <t>▼ 2,4%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1176,17 +1176,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.263,00</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 34,3%</t>
+          <t>R$ 2.818,00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>770</v>
+        <v>918</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,3%</t>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1328,24 +1328,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.969,00</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,9%</t>
+          <t>R$ 3.338,00</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>979</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,6%</t>
+        <v>903</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1474,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.637,00</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 68,9%</t>
+          <t>R$ 3.931,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▲ 20,5%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>973</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,1%</t>
+        <v>817</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,1%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1614,17 +1614,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+          <t>R$ 3.263,00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 34,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>810</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,4%</t>
+        <v>770</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,3%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1766,24 +1766,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.592,00</t>
+          <t>R$ 4.969,00</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,5%</t>
+          <t>▼ 11,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>914</v>
+        <v>979</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,5%</t>
+          <t>▲ 0,6%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1912,11 +1912,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.472,00</t>
+          <t>R$ 5.637,00</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,3%</t>
+          <t>▲ 68,9%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1057</v>
+        <v>973</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 1,7%</t>
+          <t>▲ 20,1%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2058,11 +2058,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.629,00</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,6%</t>
+          <t>R$ 3.338,00</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1075</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,7%</t>
+        <v>810</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,4%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2204,11 +2204,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.747,00</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 68,5%</t>
+          <t>R$ 3.592,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1116</v>
+        <v>914</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,7%</t>
+          <t>▼ 13,5%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2344,17 +2344,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 45,7%</t>
+          <t>R$ 3.472,00</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>973</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,1%</t>
+        <v>1057</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 1,7%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2496,24 +2496,24 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.186,00</t>
+          <t>R$ 3.629,00</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>▲ 45,7%</t>
+          <t>▼ 23,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1500</v>
+        <v>1075</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>▲ 27,9%</t>
+          <t>▼ 3,7%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2642,11 +2642,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.560,00</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,3%</t>
+          <t>R$ 4.747,00</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>▲ 68,5%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1173</v>
+        <v>1116</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,4%</t>
+          <t>▲ 14,7%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2782,9 +2782,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.412,00</t>
+          <t>R$ 2.818,00</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>▲ 17,9%</t>
+          <t>▼ 45,7%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1240</v>
+        <v>973</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,4%</t>
+          <t>▼ 35,1%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       <c r="I34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -2947,11 +2947,11 @@
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
+          <t>R$ 5.186,00</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>▼ 54,1%</t>
+          <t>▲ 45,7%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1165</v>
+        <v>1500</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 47,2%</t>
+          <t>▲ 27,9%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3080,11 +3080,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.304,00</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 117,9%</t>
+          <t>R$ 3.560,00</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>2206</v>
+        <v>1173</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▲ 101,1%</t>
+          <t>▼ 5,4%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3226,11 +3226,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,7%</t>
+          <t>R$ 3.412,00</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1097</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,0%</t>
+        <v>1240</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,4%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3372,11 +3372,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.147,00</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,9%</t>
+          <t>R$ 2.893,00</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 54,1%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>930</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,1%</t>
+        <v>1165</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 47,2%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3518,11 +3518,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.823,00</t>
+          <t>R$ 6.304,00</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,6%</t>
+          <t>▲ 117,9%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1070</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,8%</t>
+        <v>2206</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▲ 101,1%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3664,11 +3664,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,38 +3728,38 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.469,00</t>
+          <t>R$ 2.893,00</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,4%</t>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1061</v>
+        <v>1097</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,4%</t>
+          <t>▲ 18,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,33 +3874,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.708,00</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 0,9%</t>
+          <t>R$ 2.147,00</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1368</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,9%</t>
+        <v>930</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,1%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3958,9 +3958,9 @@
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4020,20 +4020,20 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.742,00</t>
+          <t>R$ 2.823,00</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,5%</t>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1485</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,6%</t>
+        <v>1070</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4042,11 +4042,11 @@
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4102,11 +4102,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,25 +4166,25 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.241,00</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,1%</t>
+          <t>R$ 3.469,00</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,4%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1211</v>
+        <v>1061</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,2%</t>
+          <t>▼ 22,4%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4248,11 +4248,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4312,33 +4312,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.072,00</t>
+          <t>R$ 3.708,00</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,1%</t>
+          <t>▼ 0,9%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1208</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 0,2%</t>
+        <v>1368</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,9%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4394,11 +4394,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4458,33 +4458,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.650,00</t>
+          <t>R$ 3.742,00</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,4%</t>
+          <t>▲ 15,5%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1211</v>
+        <v>1485</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,6%</t>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4540,11 +4540,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4604,33 +4604,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.918,00</t>
+          <t>R$ 3.241,00</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,4%</t>
+          <t>▼ 36,1%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1402</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,3%</t>
+        <v>1211</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▲ 0,2%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4686,11 +4686,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,33 +4750,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.720,00</t>
+          <t>R$ 5.072,00</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,4%</t>
+          <t>▲ 9,1%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1398</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,3%</t>
+        <v>1208</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 0,2%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4896,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.246,00</t>
+          <t>R$ 4.650,00</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>▲ 133,3%</t>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1541</v>
+        <v>1211</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,9%</t>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4978,11 +4978,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 83,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5042,33 +5042,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.677,00</t>
+          <t>R$ 5.918,00</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,0%</t>
+          <t>▲ 25,4%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1244</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,2%</t>
+        <v>1402</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▲ 0,3%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5124,11 +5124,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5188,38 +5188,38 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.523,00</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 19,3%</t>
+          <t>R$ 4.720,00</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1205</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,3%</t>
+        <v>1398</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,3%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5264,17 +5264,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5334,33 +5334,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.368,00</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,6%</t>
+          <t>R$ 6.246,00</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1344</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,9%</t>
+        <v>1541</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5416,24 +5416,24 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5480,33 +5480,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.593,00</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+          <t>R$ 2.677,00</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>▼ 24,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1319</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,8%</t>
+        <v>1244</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3,2%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5562,11 +5562,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5626,38 +5626,38 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.791,00</t>
+          <t>R$ 3.523,00</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>▲ 30,8%</t>
+          <t>▼ 19,3%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1308</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 1,4%</t>
+        <v>1205</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,3%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5702,17 +5702,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5772,38 +5772,38 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.663,00</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,8%</t>
+          <t>R$ 4.368,00</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1326</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,3%</t>
+        <v>1344</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,9%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5854,24 +5854,24 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5918,38 +5918,38 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.959,00</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 3.593,00</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1181</v>
+        <v>1319</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,9%</t>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6002,7 +6002,7 @@
       <c r="I76" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
+      <c r="J76" s="4" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
@@ -6034,12 +6034,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6064,33 +6064,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.959,00</t>
+          <t>R$ 4.791,00</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,6%</t>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1268</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,2%</t>
+        <v>1308</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▼ 1,4%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6210,20 +6210,20 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.988,00</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 94,0%</t>
+          <t>R$ 3.663,00</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>▲ 23,8%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>2156</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 105,9%</t>
+        <v>1326</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▲ 12,3%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6232,16 +6232,16 @@
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6292,11 +6292,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6356,38 +6356,38 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.086,00</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,6%</t>
+          <t>R$ 2.959,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1047</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,7%</t>
+        <v>1181</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6438,11 +6438,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6502,33 +6502,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.170,00</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+          <t>R$ 2.959,00</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1099</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,9%</t>
+        <v>1268</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 41,2%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6584,11 +6584,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6618,78 +6618,516 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 5.988,00</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>▲ 94,0%</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>2156</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▲ 105,9%</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>56,8%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.086,00</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>1047</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▼ 4,7%</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>40,2%</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.170,00</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>UTD-092</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo Inox</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>3284176106</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>R$ 4.227,00</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
+      <c r="I91" s="2" t="n">
         <v>1247</v>
       </c>
-      <c r="J85" s="2" t="inlineStr">
+      <c r="J91" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="K91" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="L85" s="2" t="n">
+      <c r="L91" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="M85" s="2" t="inlineStr">
+      <c r="M91" s="2" t="inlineStr">
         <is>
           <t>45,9%</t>
         </is>
       </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
+++ b/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
+          <t>R$ 4.497,00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,2%</t>
+          <t>▲ 16,6%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>848</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1,7%</t>
+        <v>1006</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,17 +738,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.115,00</t>
+          <t>R$ 3.857,00</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>834</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -890,24 +890,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.895,00</t>
+          <t>R$ 5.192,00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,9%</t>
+          <t>▲ 32,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>976</v>
+        <v>854</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▲ 8,9%</t>
+          <t>▲ 0,7%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,25 +1100,25 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
+          <t>R$ 3.931,00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>▲ 36,9%</t>
+          <t>▲ 26,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>896</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 2,4%</t>
+        <v>848</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1176,17 +1176,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
+          <t>R$ 3.115,00</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,6%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1,7%</t>
+        <v>834</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,5%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1328,24 +1328,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,1%</t>
+          <t>R$ 4.895,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▲ 26,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>903</v>
+        <v>976</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,5%</t>
+          <t>▲ 8,9%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1474,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
+          <t>R$ 3.857,00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>▲ 20,5%</t>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>817</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▲ 6,1%</t>
+        <v>896</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,4%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1614,17 +1614,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.263,00</t>
+          <t>R$ 2.818,00</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>▼ 34,3%</t>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>770</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,3%</t>
+        <v>918</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1766,24 +1766,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.969,00</t>
+          <t>R$ 3.338,00</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,9%</t>
+          <t>▼ 15,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>979</v>
+        <v>903</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▲ 0,6%</t>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1912,11 +1912,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.637,00</t>
+          <t>R$ 3.931,00</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>▲ 68,9%</t>
+          <t>▲ 20,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>973</v>
+        <v>817</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▲ 20,1%</t>
+          <t>▲ 6,1%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2052,17 +2052,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
+          <t>R$ 3.263,00</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,1%</t>
+          <t>▼ 34,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>810</v>
+        <v>770</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,4%</t>
+          <t>▼ 21,3%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2204,24 +2204,24 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.592,00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▲ 3,5%</t>
+          <t>R$ 4.969,00</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>914</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,5%</t>
+        <v>979</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▲ 0,6%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2350,11 +2350,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.472,00</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,3%</t>
+          <t>R$ 5.637,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▲ 68,9%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1057</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 1,7%</t>
+        <v>973</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▲ 20,1%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2496,11 +2496,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.629,00</t>
+          <t>R$ 3.338,00</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,6%</t>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1075</v>
+        <v>810</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>▼ 3,7%</t>
+          <t>▼ 11,4%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2642,11 +2642,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.747,00</t>
+          <t>R$ 3.592,00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>▲ 68,5%</t>
+          <t>▲ 3,5%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1116</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▲ 14,7%</t>
+        <v>914</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,5%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2782,17 +2782,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
+          <t>R$ 3.472,00</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>▼ 45,7%</t>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>973</v>
+        <v>1057</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▼ 35,1%</t>
+          <t>▼ 1,7%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2934,24 +2934,24 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.186,00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▲ 45,7%</t>
+          <t>R$ 3.629,00</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 23,6%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▲ 27,9%</t>
+        <v>1075</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 3,7%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3080,11 +3080,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.560,00</t>
+          <t>R$ 4.747,00</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>▲ 4,3%</t>
+          <t>▲ 68,5%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1173</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▼ 5,4%</t>
+        <v>1116</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,7%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3220,9 +3220,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.412,00</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>▲ 17,9%</t>
+          <t>R$ 2.818,00</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>▼ 45,7%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▲ 6,4%</t>
+        <v>973</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▼ 35,1%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3385,11 +3385,11 @@
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 54,1%</t>
+          <t>R$ 5.186,00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▲ 45,7%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1165</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 47,2%</t>
+        <v>1500</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▲ 27,9%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3518,11 +3518,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.304,00</t>
+          <t>R$ 3.560,00</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>▲ 117,9%</t>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>2206</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▲ 101,1%</t>
+        <v>1173</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,4%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3664,11 +3664,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
+          <t>R$ 3.412,00</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>▲ 34,7%</t>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1097</v>
+        <v>1240</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>▲ 18,0%</t>
+          <t>▲ 6,4%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3810,11 +3810,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,33 +3874,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.147,00</t>
+          <t>R$ 2.893,00</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▼ 54,1%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>930</v>
+        <v>1165</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,1%</t>
+          <t>▼ 47,2%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3956,11 +3956,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4020,33 +4020,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.823,00</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,6%</t>
+          <t>R$ 6.304,00</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▲ 117,9%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1070</v>
+        <v>2206</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>▲ 0,8%</t>
+          <t>▲ 101,1%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4102,11 +4102,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,38 +4166,38 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.469,00</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,4%</t>
+          <t>R$ 2.893,00</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1061</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▼ 22,4%</t>
+        <v>1097</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▲ 18,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4312,33 +4312,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.708,00</t>
+          <t>R$ 2.147,00</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>▼ 0,9%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1368</v>
+        <v>930</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,9%</t>
+          <t>▼ 13,1%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4396,9 +4396,9 @@
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4458,20 +4458,20 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.742,00</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>▲ 15,5%</t>
+          <t>R$ 2.823,00</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1485</v>
+        <v>1070</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,6%</t>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4480,11 +4480,11 @@
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4540,11 +4540,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4604,25 +4604,25 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.241,00</t>
+          <t>R$ 3.469,00</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,1%</t>
+          <t>▼ 6,4%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1211</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▲ 0,2%</t>
+        <v>1061</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▼ 22,4%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4686,11 +4686,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,33 +4750,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.072,00</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>▲ 9,1%</t>
+          <t>R$ 3.708,00</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 0,9%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1208</v>
+        <v>1368</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>▼ 0,2%</t>
+          <t>▼ 7,9%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4832,11 +4832,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4896,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.650,00</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,4%</t>
+          <t>R$ 3.742,00</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>▲ 15,5%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1211</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,6%</t>
+        <v>1485</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4978,11 +4978,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5042,33 +5042,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.918,00</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,4%</t>
+          <t>R$ 3.241,00</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,1%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1402</v>
+        <v>1211</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▲ 0,3%</t>
+          <t>▲ 0,2%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5124,11 +5124,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5188,33 +5188,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.720,00</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,4%</t>
+          <t>R$ 5.072,00</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>▲ 9,1%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1398</v>
+        <v>1208</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>▼ 9,3%</t>
+          <t>▼ 0,2%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5272,9 +5272,9 @@
       <c r="I66" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5334,33 +5334,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.246,00</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+          <t>R$ 4.650,00</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1541</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▲ 23,9%</t>
+        <v>1211</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5416,11 +5416,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5480,33 +5480,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.677,00</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,0%</t>
+          <t>R$ 5.918,00</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,4%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1244</v>
+        <v>1402</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▲ 3,2%</t>
+          <t>▲ 0,3%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5562,11 +5562,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5626,38 +5626,38 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.523,00</t>
+          <t>R$ 4.720,00</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>▼ 19,3%</t>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1205</v>
+        <v>1398</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,3%</t>
+          <t>▼ 9,3%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5702,17 +5702,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5772,33 +5772,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.368,00</t>
+          <t>R$ 6.246,00</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>▲ 21,6%</t>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1344</v>
+        <v>1541</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▲ 1,9%</t>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5854,24 +5854,24 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5918,33 +5918,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.593,00</t>
+          <t>R$ 2.677,00</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 24,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1319</v>
+        <v>1244</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>▲ 0,8%</t>
+          <t>▲ 3,2%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6000,11 +6000,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6064,38 +6064,38 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.791,00</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▲ 30,8%</t>
+          <t>R$ 3.523,00</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>▼ 19,3%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1308</v>
+        <v>1205</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>▼ 1,4%</t>
+          <t>▼ 10,3%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6140,17 +6140,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6210,38 +6210,38 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.663,00</t>
+          <t>R$ 4.368,00</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>▲ 23,8%</t>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1326</v>
+        <v>1344</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>▲ 12,3%</t>
+          <t>▲ 1,9%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6292,24 +6292,24 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6356,38 +6356,38 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.959,00</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 3.593,00</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1181</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>1319</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6502,33 +6502,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.959,00</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+          <t>R$ 4.791,00</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1268</v>
+        <v>1308</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>▼ 41,2%</t>
+          <t>▼ 1,4%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6648,20 +6648,20 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.988,00</t>
+          <t>R$ 3.663,00</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>▲ 94,0%</t>
+          <t>▲ 23,8%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>2156</v>
+        <v>1326</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>▲ 105,9%</t>
+          <t>▲ 12,3%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6670,16 +6670,16 @@
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6730,11 +6730,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6764,12 +6764,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6794,38 +6794,38 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.086,00</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="inlineStr">
-        <is>
-          <t>▼ 2,6%</t>
+          <t>R$ 2.959,00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1047</v>
+        <v>1181</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>▼ 4,7%</t>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6876,11 +6876,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6940,33 +6940,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.170,00</t>
+          <t>R$ 2.959,00</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1099</v>
+        <v>1268</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,9%</t>
+          <t>▼ 41,2%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7022,11 +7022,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7056,78 +7056,516 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 5.988,00</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>▲ 94,0%</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>2156</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▲ 105,9%</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>56,8%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.086,00</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>1047</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▼ 4,7%</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>40,2%</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.170,00</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>UTD-092</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo Inox</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>3284176106</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>R$ 4.227,00</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="n">
+      <c r="I97" s="2" t="n">
         <v>1247</v>
       </c>
-      <c r="J91" s="2" t="inlineStr">
+      <c r="J97" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K91" s="2" t="inlineStr">
+      <c r="K97" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="L91" s="2" t="n">
+      <c r="L97" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="M91" s="2" t="inlineStr">
+      <c r="M97" s="2" t="inlineStr">
         <is>
           <t>45,9%</t>
         </is>
       </c>
-      <c r="N91" s="2" t="inlineStr">
+      <c r="N97" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
+++ b/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.497,00</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▲ 16,6%</t>
+          <t>R$ 4.239,00</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,7%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1006</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>937</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,7%</t>
+          <t>R$ 4.497,00</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1006</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.192,00</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▲ 32,1%</t>
+          <t>R$ 3.857,00</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>854</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▲ 0,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1038,9 +1038,9 @@
       <c r="I8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
+          <t>R$ 5.192,00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,2%</t>
+          <t>▲ 32,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▲ 1,7%</t>
+          <t>▲ 0,7%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1176,17 +1176,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.115,00</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+          <t>R$ 3.931,00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▲ 26,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>834</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,5%</t>
+        <v>848</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.895,00</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▲ 26,9%</t>
+          <t>R$ 3.115,00</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>976</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▲ 8,9%</t>
+        <v>834</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,5%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1474,24 +1474,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
+          <t>R$ 4.895,00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>▲ 36,9%</t>
+          <t>▲ 26,9%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>896</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▼ 2,4%</t>
+        <v>976</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▲ 8,9%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1620,11 +1620,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+          <t>R$ 3.857,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1,7%</t>
+        <v>896</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,4%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1768,9 +1768,9 @@
       <c r="I18" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
+          <t>R$ 2.818,00</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,1%</t>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>903</v>
+        <v>918</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,5%</t>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1912,11 +1912,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▲ 20,5%</t>
+          <t>R$ 3.338,00</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>817</v>
+        <v>903</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▲ 6,1%</t>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2052,17 +2052,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.263,00</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 34,3%</t>
+          <t>R$ 3.931,00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▲ 20,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>770</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,3%</t>
+        <v>817</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,1%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.969,00</t>
+          <t>R$ 3.263,00</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,9%</t>
+          <t>▼ 34,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>979</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▲ 0,6%</t>
+        <v>770</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,3%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2350,24 +2350,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.637,00</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▲ 68,9%</t>
+          <t>R$ 4.969,00</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▲ 20,1%</t>
+          <t>▲ 0,6%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2496,11 +2496,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+          <t>R$ 5.637,00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▲ 68,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>810</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,4%</t>
+        <v>973</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▲ 20,1%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2642,11 +2642,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2706,25 +2706,25 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.592,00</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▲ 3,5%</t>
+          <t>R$ 3.338,00</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>914</v>
+        <v>810</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,5%</t>
+          <t>▼ 11,4%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2788,11 +2788,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.472,00</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,3%</t>
+          <t>R$ 3.592,00</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3,5%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1057</v>
+        <v>914</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▼ 1,7%</t>
+          <t>▼ 13,5%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2934,11 +2934,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.629,00</t>
+          <t>R$ 3.472,00</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,6%</t>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1075</v>
+        <v>1057</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>▼ 3,7%</t>
+          <t>▼ 1,7%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.747,00</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>▲ 68,5%</t>
+          <t>R$ 3.629,00</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 23,6%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1116</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▲ 14,7%</t>
+        <v>1075</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 3,7%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3220,17 +3220,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>▼ 45,7%</t>
+          <t>R$ 4.747,00</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>▲ 68,5%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>973</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▼ 35,1%</t>
+        <v>1116</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,7%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3363,33 +3363,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.186,00</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>▲ 45,7%</t>
+          <t>R$ 2.818,00</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 45,7%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▲ 27,9%</t>
+        <v>973</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 35,1%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3518,11 +3518,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3531,11 +3531,11 @@
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.560,00</t>
+          <t>R$ 5.186,00</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>▲ 4,3%</t>
+          <t>▲ 45,7%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1173</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▼ 5,4%</t>
+        <v>1500</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▲ 27,9%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,14 +3625,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3664,11 +3664,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,14 +3698,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.412,00</t>
+          <t>R$ 3.560,00</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>▲ 17,9%</t>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▲ 6,4%</t>
+        <v>1173</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,4%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,14 +3771,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3810,11 +3810,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3844,14 +3844,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3874,33 +3874,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>▼ 54,1%</t>
+          <t>R$ 3.412,00</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1165</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▼ 47,2%</t>
+        <v>1240</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,4%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,14 +3917,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3956,11 +3956,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3990,14 +3990,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4020,33 +4020,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.304,00</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>▲ 117,9%</t>
+          <t>R$ 2.893,00</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>▼ 54,1%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>2206</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▲ 101,1%</t>
+        <v>1165</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▼ 47,2%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,14 +4063,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4102,11 +4102,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,14 +4136,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4166,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
+          <t>R$ 6.304,00</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>▲ 34,7%</t>
+          <t>▲ 117,9%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1097</v>
+        <v>2206</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>▲ 18,0%</t>
+          <t>▲ 101,1%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4282,14 +4282,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4312,33 +4312,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.147,00</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>▼ 23,9%</t>
+          <t>R$ 2.893,00</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>930</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,1%</t>
+        <v>1097</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▲ 18,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,14 +4355,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4394,11 +4394,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,14 +4428,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4458,33 +4458,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.823,00</t>
+          <t>R$ 2.147,00</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>▼ 18,6%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1070</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▲ 0,8%</t>
+        <v>930</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,1%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,14 +4501,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4540,11 +4540,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4574,14 +4574,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4604,38 +4604,38 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.469,00</t>
+          <t>R$ 2.823,00</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,4%</t>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1061</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▼ 22,4%</t>
+        <v>1070</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4647,14 +4647,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4686,11 +4686,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4720,14 +4720,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4750,38 +4750,38 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.708,00</t>
+          <t>R$ 3.469,00</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>▼ 0,9%</t>
+          <t>▼ 6,4%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1368</v>
+        <v>1061</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,9%</t>
+          <t>▼ 22,4%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -4793,14 +4793,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4866,14 +4866,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4896,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.742,00</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>▲ 15,5%</t>
+          <t>R$ 3.708,00</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>▼ 0,9%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1485</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▲ 22,6%</t>
+        <v>1368</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,9%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5012,14 +5012,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5042,33 +5042,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.241,00</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>▼ 36,1%</t>
+          <t>R$ 3.742,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▲ 15,5%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1211</v>
+        <v>1485</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▲ 0,2%</t>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5126,9 +5126,9 @@
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5158,14 +5158,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5188,33 +5188,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.072,00</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>▲ 9,1%</t>
+          <t>R$ 3.241,00</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,1%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1208</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 0,2%</t>
+        <v>1211</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▲ 0,2%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,14 +5231,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5270,11 +5270,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5304,14 +5304,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5334,33 +5334,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.650,00</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,4%</t>
+          <t>R$ 5.072,00</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>▲ 9,1%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,6%</t>
+          <t>▼ 0,2%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,14 +5377,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5416,11 +5416,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5450,14 +5450,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5480,33 +5480,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.918,00</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,4%</t>
+          <t>R$ 4.650,00</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1402</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▲ 0,3%</t>
+        <v>1211</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,14 +5523,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5562,11 +5562,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5596,14 +5596,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5626,33 +5626,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.720,00</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,4%</t>
+          <t>R$ 5.918,00</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,4%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1398</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▼ 9,3%</t>
+        <v>1402</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▲ 0,3%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,14 +5669,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5708,11 +5708,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5742,14 +5742,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5772,33 +5772,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.246,00</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+          <t>R$ 4.720,00</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1541</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▲ 23,9%</t>
+        <v>1398</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,3%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,14 +5815,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5854,11 +5854,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5888,14 +5888,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5918,33 +5918,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.677,00</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,0%</t>
+          <t>R$ 6.246,00</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1244</v>
+        <v>1541</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>▲ 3,2%</t>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,14 +5961,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6000,11 +6000,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6034,14 +6034,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6064,38 +6064,38 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.523,00</t>
+          <t>R$ 2.677,00</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>▼ 19,3%</t>
+          <t>▼ 24,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1205</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,3%</t>
+        <v>1244</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3,2%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -6107,14 +6107,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6140,17 +6140,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6180,14 +6180,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6210,38 +6210,38 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.368,00</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>▲ 21,6%</t>
+          <t>R$ 3.523,00</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>▼ 19,3%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1344</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1,9%</t>
+        <v>1205</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,3%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6253,14 +6253,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6283,33 +6283,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6326,14 +6326,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6356,33 +6356,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.593,00</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+          <t>R$ 4.368,00</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1319</v>
+        <v>1344</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>▲ 0,8%</t>
+          <t>▲ 1,9%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6399,14 +6399,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6438,24 +6438,24 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6472,14 +6472,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6502,33 +6502,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.791,00</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>▲ 30,8%</t>
+          <t>R$ 3.593,00</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1308</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▼ 1,4%</t>
+        <v>1319</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6545,14 +6545,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6584,11 +6584,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6618,14 +6618,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6648,38 +6648,38 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.663,00</t>
+          <t>R$ 4.791,00</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>▲ 23,8%</t>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1326</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▲ 12,3%</t>
+        <v>1308</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▼ 1,4%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
@@ -6691,14 +6691,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6730,11 +6730,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6764,14 +6764,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6794,33 +6794,33 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.959,00</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 3.663,00</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>▲ 23,8%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1181</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>1326</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▲ 12,3%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6837,14 +6837,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6876,11 +6876,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6910,14 +6910,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6943,35 +6943,35 @@
           <t>R$ 2.959,00</t>
         </is>
       </c>
-      <c r="H89" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1268</v>
+        <v>1181</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>▼ 41,2%</t>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
@@ -6983,14 +6983,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7022,11 +7022,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7056,14 +7056,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7086,33 +7086,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.988,00</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>▲ 94,0%</t>
+          <t>R$ 2.959,00</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>2156</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▲ 105,9%</t>
+        <v>1268</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▼ 41,2%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7170,9 +7170,9 @@
       <c r="I92" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7202,14 +7202,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7232,33 +7232,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.086,00</t>
-        </is>
-      </c>
-      <c r="H93" s="4" t="inlineStr">
-        <is>
-          <t>▼ 2,6%</t>
+          <t>R$ 5.988,00</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▲ 94,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1047</v>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,7%</t>
+        <v>2156</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▲ 105,9%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7275,14 +7275,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7314,11 +7314,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7348,14 +7348,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7378,20 +7378,20 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.170,00</t>
+          <t>R$ 3.086,00</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1099</v>
+        <v>1047</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,9%</t>
+          <t>▼ 4,7%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7400,11 +7400,11 @@
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7421,14 +7421,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7460,11 +7460,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7494,78 +7494,224 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.170,00</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>UTD-092</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo Inox</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>3284176106</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>R$ 4.227,00</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
+      <c r="I99" s="2" t="n">
         <v>1247</v>
       </c>
-      <c r="J97" s="2" t="inlineStr">
+      <c r="J99" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K97" s="2" t="inlineStr">
+      <c r="K99" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="L97" s="2" t="n">
+      <c r="L99" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="M97" s="2" t="inlineStr">
+      <c r="M99" s="2" t="inlineStr">
         <is>
           <t>45,9%</t>
         </is>
       </c>
-      <c r="N97" s="2" t="inlineStr">
+      <c r="N99" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O97" s="2" t="inlineStr">
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
+++ b/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.239,00</t>
+          <t>R$ 4.599,00</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>▼ 5,7%</t>
+          <t>▲ 21,4%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>937</v>
+        <v>1062</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,9%</t>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.497,00</t>
+          <t>R$ 3.787,00</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,6%</t>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1006</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>941</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,4%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,7%</t>
+          <t>R$ 4.239,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>937</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.192,00</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▲ 32,1%</t>
+          <t>R$ 4.497,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>854</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▲ 0,7%</t>
+        <v>1006</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
+          <t>R$ 3.857,00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,2%</t>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>848</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▲ 1,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.115,00</t>
+          <t>R$ 5.192,00</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▲ 32,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>834</v>
+        <v>854</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,5%</t>
+          <t>▲ 0,7%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1474,24 +1474,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.895,00</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▲ 26,9%</t>
+          <t>R$ 3.931,00</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,2%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>976</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▲ 8,9%</t>
+        <v>848</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1614,17 +1614,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
+          <t>R$ 3.115,00</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>▲ 36,9%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>896</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 2,4%</t>
+        <v>834</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,5%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1766,24 +1766,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
+          <t>R$ 4.895,00</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,6%</t>
+          <t>▲ 26,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1,7%</t>
+        <v>976</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,9%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1912,11 +1912,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>2</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
+          <t>R$ 3.857,00</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,1%</t>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,5%</t>
+          <t>▼ 2,4%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2058,11 +2058,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
+          <t>R$ 2.818,00</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>▲ 20,5%</t>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>817</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▲ 6,1%</t>
+        <v>918</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2198,17 +2198,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.263,00</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 34,3%</t>
+          <t>R$ 3.338,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>770</v>
+        <v>903</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>▼ 21,3%</t>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2350,24 +2350,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.969,00</t>
+          <t>R$ 3.931,00</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,9%</t>
+          <t>▲ 20,5%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>979</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▲ 0,6%</t>
+        <v>817</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,1%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2490,9 +2490,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.637,00</t>
+          <t>R$ 3.263,00</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>▲ 68,9%</t>
+          <t>▼ 34,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>973</v>
+        <v>770</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>▲ 20,1%</t>
+          <t>▼ 21,3%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2642,24 +2642,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+          <t>R$ 4.969,00</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>810</v>
+        <v>979</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,4%</t>
+          <t>▲ 0,6%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2788,11 +2788,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.592,00</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>▲ 3,5%</t>
+          <t>R$ 5.637,00</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 68,9%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>914</v>
+        <v>973</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,5%</t>
+          <t>▲ 20,1%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2934,11 +2934,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.472,00</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,3%</t>
+          <t>R$ 3.338,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1057</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 1,7%</t>
+        <v>810</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,4%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3080,11 +3080,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.629,00</t>
+          <t>R$ 3.592,00</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,6%</t>
+          <t>▲ 3,5%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1075</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▼ 3,7%</t>
+        <v>914</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,5%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3226,11 +3226,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.747,00</t>
+          <t>R$ 3.472,00</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>▲ 68,5%</t>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1116</v>
+        <v>1057</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,7%</t>
+          <t>▼ 1,7%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3366,17 +3366,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 45,7%</t>
+          <t>R$ 3.629,00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,6%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>973</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 35,1%</t>
+        <v>1075</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,7%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3518,24 +3518,24 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.186,00</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>▲ 45,7%</t>
+          <t>R$ 4.747,00</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 68,5%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▲ 27,9%</t>
+        <v>1116</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,7%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3658,17 +3658,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.560,00</t>
+          <t>R$ 2.818,00</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>▲ 4,3%</t>
+          <t>▼ 45,7%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1173</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▼ 5,4%</t>
+        <v>973</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,1%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3810,24 +3810,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,33 +3874,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.412,00</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>▲ 17,9%</t>
+          <t>R$ 5.186,00</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 45,7%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▲ 6,4%</t>
+        <v>1500</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27,9%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3956,11 +3956,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4020,33 +4020,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
+          <t>R$ 3.560,00</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>▼ 54,1%</t>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1165</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▼ 47,2%</t>
+        <v>1173</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,4%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4104,9 +4104,9 @@
       <c r="I50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.304,00</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>▲ 117,9%</t>
+          <t>R$ 3.412,00</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>2206</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▲ 101,1%</t>
+        <v>1240</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,4%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4248,11 +4248,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4317,20 +4317,20 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>▲ 34,7%</t>
+          <t>▼ 54,1%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1097</v>
+        <v>1165</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>▲ 18,0%</t>
+          <t>▼ 47,2%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4394,11 +4394,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4458,33 +4458,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.147,00</t>
+          <t>R$ 6.304,00</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▲ 117,9%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>930</v>
+        <v>2206</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,1%</t>
+          <t>▲ 101,1%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4540,11 +4540,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4604,20 +4604,20 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.823,00</t>
+          <t>R$ 2.893,00</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>▼ 18,6%</t>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1070</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▲ 0,8%</t>
+        <v>1097</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4626,11 +4626,11 @@
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4686,11 +4686,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,38 +4750,38 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.469,00</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,4%</t>
+          <t>R$ 2.147,00</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1061</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 22,4%</t>
+        <v>930</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,1%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4832,11 +4832,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4896,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.708,00</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>▼ 0,9%</t>
+          <t>R$ 2.823,00</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1368</v>
+        <v>1070</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,9%</t>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4978,11 +4978,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5042,38 +5042,38 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.742,00</t>
+          <t>R$ 3.469,00</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>▲ 15,5%</t>
+          <t>▼ 6,4%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1485</v>
+        <v>1061</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,6%</t>
+          <t>▼ 22,4%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5188,33 +5188,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.241,00</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 36,1%</t>
+          <t>R$ 3.708,00</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,9%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1211</v>
+        <v>1368</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▲ 0,2%</t>
+          <t>▼ 7,9%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5272,9 +5272,9 @@
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5334,33 +5334,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.072,00</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>▲ 9,1%</t>
+          <t>R$ 3.742,00</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,5%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1208</v>
+        <v>1485</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▼ 0,2%</t>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5416,11 +5416,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.650,00</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,4%</t>
+          <t>R$ 3.241,00</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,1%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
@@ -5493,20 +5493,20 @@
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,6%</t>
+          <t>▲ 0,2%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5562,11 +5562,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5626,33 +5626,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.918,00</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,4%</t>
+          <t>R$ 5.072,00</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,1%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1402</v>
+        <v>1208</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▲ 0,3%</t>
+          <t>▼ 0,2%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5708,11 +5708,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5772,33 +5772,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.720,00</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,4%</t>
+          <t>R$ 4.650,00</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1398</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 9,3%</t>
+        <v>1211</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5854,11 +5854,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5918,20 +5918,20 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.246,00</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+          <t>R$ 5.918,00</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,4%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1541</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▲ 23,9%</t>
+        <v>1402</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,3%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5940,11 +5940,11 @@
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6000,11 +6000,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6064,33 +6064,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.677,00</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,0%</t>
+          <t>R$ 4.720,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1244</v>
+        <v>1398</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▲ 3,2%</t>
+          <t>▼ 9,3%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6146,11 +6146,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6210,38 +6210,38 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.523,00</t>
+          <t>R$ 6.246,00</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>▼ 19,3%</t>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1205</v>
+        <v>1541</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,3%</t>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6286,17 +6286,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6356,33 +6356,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.368,00</t>
+          <t>R$ 2.677,00</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>▲ 21,6%</t>
+          <t>▼ 24,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1344</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1,9%</t>
+        <v>1244</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,2%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6438,24 +6438,24 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6502,25 +6502,25 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.593,00</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+          <t>R$ 3.523,00</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 19,3%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1319</v>
+        <v>1205</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>▲ 0,8%</t>
+          <t>▼ 10,3%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6578,17 +6578,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6648,33 +6648,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.791,00</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>▲ 30,8%</t>
+          <t>R$ 4.368,00</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1308</v>
+        <v>1344</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>▼ 1,4%</t>
+          <t>▲ 1,9%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6730,24 +6730,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6764,12 +6764,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6794,20 +6794,20 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.663,00</t>
+          <t>R$ 3.593,00</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>▲ 23,8%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1326</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▲ 12,3%</t>
+        <v>1319</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6816,16 +6816,16 @@
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6876,11 +6876,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6940,38 +6940,38 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.959,00</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 4.791,00</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1181</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>1308</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 1,4%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7022,11 +7022,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7056,12 +7056,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7086,38 +7086,38 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.959,00</t>
+          <t>R$ 3.663,00</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,6%</t>
+          <t>▲ 23,8%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1268</v>
+        <v>1326</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>▼ 41,2%</t>
+          <t>▲ 12,3%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7168,11 +7168,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7232,38 +7232,38 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.988,00</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>▲ 94,0%</t>
+          <t>R$ 2.959,00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>2156</v>
+        <v>1181</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>▲ 105,9%</t>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7314,11 +7314,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7378,33 +7378,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.086,00</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t>▼ 2,6%</t>
+          <t>R$ 2.959,00</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1047</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,7%</t>
+        <v>1268</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,2%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7460,11 +7460,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7524,33 +7524,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.170,00</t>
+          <t>R$ 5.988,00</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 94,0%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>1099</v>
+        <v>2156</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,9%</t>
+          <t>▲ 105,9%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7567,12 +7567,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7606,11 +7606,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7640,78 +7640,370 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.086,00</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>1047</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,7%</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>40,2%</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.170,00</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>UTD-092</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo Inox</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>3284176106</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>R$ 4.227,00</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="n">
+      <c r="I103" s="2" t="n">
         <v>1247</v>
       </c>
-      <c r="J99" s="2" t="inlineStr">
+      <c r="J103" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K99" s="2" t="inlineStr">
+      <c r="K103" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="L99" s="2" t="n">
+      <c r="L103" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="M99" s="2" t="inlineStr">
+      <c r="M103" s="2" t="inlineStr">
         <is>
           <t>45,9%</t>
         </is>
       </c>
-      <c r="N99" s="2" t="inlineStr">
+      <c r="N103" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O99" s="2" t="inlineStr">
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
+++ b/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.599,00</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,4%</t>
+          <t>R$ 3.857,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,8%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1062</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,9%</t>
+        <v>958</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.787,00</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,7%</t>
+          <t>R$ 4.228,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>941</v>
+        <v>1001</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,4%</t>
+          <t>▲ 3,4%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.239,00</t>
+          <t>R$ 3.709,00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,7%</t>
+          <t>▼ 3,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>937</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>968</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,8%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.497,00</t>
+          <t>R$ 3.857,00</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,6%</t>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1006</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>915</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
+          <t>R$ 3.263,00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,7%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>976</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,5%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1328,11 +1328,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.192,00</t>
+          <t>R$ 4.079,00</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>▲ 32,1%</t>
+          <t>▲ 44,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>854</v>
+        <v>943</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,7%</t>
+          <t>▲ 9,1%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1474,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,2%</t>
+          <t>R$ 2.818,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,7%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>848</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,7%</t>
+        <v>864</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,4%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1614,17 +1614,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.115,00</t>
+          <t>R$ 3.598,00</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▼ 1,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>834</v>
+        <v>885</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,5%</t>
+          <t>▼ 18,4%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1766,24 +1766,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.895,00</t>
+          <t>R$ 3.634,00</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,9%</t>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>976</v>
+        <v>1085</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,9%</t>
+          <t>▲ 8,4%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1912,11 +1912,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 36,9%</t>
+          <t>R$ 3.486,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,9%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>896</v>
+        <v>1001</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,4%</t>
+          <t>▼ 2,1%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2060,9 +2060,9 @@
       <c r="I22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+          <t>R$ 4.524,00</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,7%</t>
+        <v>1022</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 1,7%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2204,11 +2204,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,5%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
+          <t>R$ 4.450,00</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,1%</t>
+          <t>▼ 3,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>903</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,5%</t>
+        <v>1040</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,1%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2350,11 +2350,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
+          <t>R$ 4.599,00</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,5%</t>
+          <t>▲ 21,4%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>817</v>
+        <v>1062</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,1%</t>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2490,17 +2490,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.263,00</t>
+          <t>R$ 3.787,00</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>▼ 34,3%</t>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>770</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,3%</t>
+        <v>941</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,4%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2642,24 +2642,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.969,00</t>
+          <t>R$ 4.239,00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,9%</t>
+          <t>▼ 5,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>979</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,6%</t>
+        <v>937</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2790,9 +2790,9 @@
       <c r="I32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,29 +2852,29 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.637,00</t>
+          <t>R$ 4.497,00</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>▲ 68,9%</t>
+          <t>▲ 16,6%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>973</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,1%</t>
+        <v>1006</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2934,11 +2934,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
+          <t>R$ 3.857,00</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,1%</t>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3080,11 +3080,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.592,00</t>
+          <t>R$ 5.192,00</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,5%</t>
+          <t>▲ 32,1%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>914</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,5%</t>
+        <v>854</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,7%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3226,11 +3226,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.472,00</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,3%</t>
+          <t>R$ 3.931,00</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,2%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1057</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 1,7%</t>
+        <v>848</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3366,17 +3366,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.629,00</t>
+          <t>R$ 3.115,00</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,6%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1075</v>
+        <v>834</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,7%</t>
+          <t>▼ 14,5%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3518,24 +3518,24 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.747,00</t>
+          <t>R$ 4.895,00</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>▲ 68,5%</t>
+          <t>▲ 26,9%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1116</v>
+        <v>976</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,7%</t>
+          <t>▲ 8,9%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3658,17 +3658,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 45,7%</t>
+          <t>R$ 3.857,00</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>973</v>
+        <v>896</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>▼ 35,1%</t>
+          <t>▼ 2,4%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3810,24 +3810,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,33 +3874,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.186,00</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 45,7%</t>
+          <t>R$ 2.818,00</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1500</v>
+        <v>918</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>▲ 27,9%</t>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3958,9 +3958,9 @@
       <c r="I48" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4020,33 +4020,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.560,00</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,3%</t>
+          <t>R$ 3.338,00</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,1%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1173</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,4%</t>
+        <v>903</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4102,11 +4102,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.412,00</t>
+          <t>R$ 3.931,00</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>▲ 17,9%</t>
+          <t>▲ 20,5%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1240</v>
+        <v>817</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,4%</t>
+          <t>▲ 6,1%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4242,17 +4242,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4312,33 +4312,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
+          <t>R$ 3.263,00</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>▼ 54,1%</t>
+          <t>▼ 34,3%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1165</v>
+        <v>770</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>▼ 47,2%</t>
+          <t>▼ 21,3%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4394,24 +4394,24 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4458,33 +4458,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.304,00</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 117,9%</t>
+          <t>R$ 4.969,00</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>2206</v>
+        <v>979</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>▲ 101,1%</t>
+          <t>▲ 0,6%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4540,11 +4540,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4604,33 +4604,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
+          <t>R$ 5.637,00</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>▲ 34,7%</t>
+          <t>▲ 68,9%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1097</v>
+        <v>973</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,0%</t>
+          <t>▲ 20,1%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,33 +4750,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.147,00</t>
+          <t>R$ 3.338,00</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>930</v>
+        <v>810</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,1%</t>
+          <t>▼ 11,4%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4896,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.823,00</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,6%</t>
+          <t>R$ 3.592,00</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,5%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1070</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,8%</t>
+        <v>914</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,5%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4978,11 +4978,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5042,38 +5042,38 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.469,00</t>
+          <t>R$ 3.472,00</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,4%</t>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,4%</t>
+          <t>▼ 1,7%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5126,9 +5126,9 @@
       <c r="I64" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5188,33 +5188,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.708,00</t>
+          <t>R$ 3.629,00</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>▼ 0,9%</t>
+          <t>▼ 23,6%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1368</v>
+        <v>1075</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,9%</t>
+          <t>▼ 3,7%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5270,11 +5270,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5334,33 +5334,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.742,00</t>
+          <t>R$ 4.747,00</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,5%</t>
+          <t>▲ 68,5%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1485</v>
+        <v>1116</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,6%</t>
+          <t>▲ 14,7%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5410,13 +5410,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5450,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5480,33 +5480,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.241,00</t>
+          <t>R$ 2.818,00</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,1%</t>
+          <t>▼ 45,7%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1211</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,2%</t>
+        <v>973</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,1%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5575,11 +5575,11 @@
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5626,33 +5626,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.072,00</t>
+          <t>R$ 5.186,00</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,1%</t>
+          <t>▲ 45,7%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1208</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 0,2%</t>
+        <v>1500</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27,9%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5710,9 +5710,9 @@
       <c r="I72" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5772,33 +5772,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.650,00</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,4%</t>
+          <t>R$ 3.560,00</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1211</v>
+        <v>1173</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,6%</t>
+          <t>▼ 5,4%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5854,11 +5854,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5918,33 +5918,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.918,00</t>
+          <t>R$ 3.412,00</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,4%</t>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1402</v>
+        <v>1240</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,3%</t>
+          <t>▲ 6,4%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6000,11 +6000,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6064,33 +6064,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.720,00</t>
+          <t>R$ 2.893,00</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,4%</t>
+          <t>▼ 54,1%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1398</v>
+        <v>1165</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,3%</t>
+          <t>▼ 47,2%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6146,11 +6146,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6210,33 +6210,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.246,00</t>
+          <t>R$ 6.304,00</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>▲ 133,3%</t>
+          <t>▲ 117,9%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1541</v>
+        <v>2206</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,9%</t>
+          <t>▲ 101,1%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6292,11 +6292,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6356,33 +6356,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.677,00</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,0%</t>
+          <t>R$ 2.893,00</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1244</v>
+        <v>1097</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,2%</t>
+          <t>▲ 18,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6438,11 +6438,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6502,38 +6502,38 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.523,00</t>
+          <t>R$ 2.147,00</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>▼ 19,3%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1205</v>
+        <v>930</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,3%</t>
+          <t>▼ 13,1%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6578,17 +6578,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6648,33 +6648,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.368,00</t>
-        </is>
-      </c>
-      <c r="H85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,6%</t>
+          <t>R$ 2.823,00</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1344</v>
+        <v>1070</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,9%</t>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6730,24 +6730,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6764,12 +6764,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6794,38 +6794,38 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.593,00</t>
+          <t>R$ 3.469,00</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 6,4%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1319</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,8%</t>
+        <v>1061</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,4%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6876,11 +6876,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6940,33 +6940,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.791,00</t>
-        </is>
-      </c>
-      <c r="H89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 30,8%</t>
+          <t>R$ 3.708,00</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,9%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1308</v>
+        <v>1368</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>▼ 1,4%</t>
+          <t>▼ 7,9%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7056,12 +7056,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7086,38 +7086,38 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.663,00</t>
+          <t>R$ 3.742,00</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,8%</t>
+          <t>▲ 15,5%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1326</v>
+        <v>1485</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,3%</t>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7170,9 +7170,9 @@
       <c r="I92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7232,38 +7232,38 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.959,00</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 3.241,00</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,1%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1181</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>1211</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,2%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7314,11 +7314,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7378,33 +7378,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.959,00</t>
-        </is>
-      </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+          <t>R$ 5.072,00</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,1%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1268</v>
+        <v>1208</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,2%</t>
+          <t>▼ 0,2%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7460,11 +7460,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7524,33 +7524,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.988,00</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>▲ 94,0%</t>
+          <t>R$ 4.650,00</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>2156</v>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>▲ 105,9%</t>
+        <v>1211</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7567,12 +7567,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7606,11 +7606,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7670,33 +7670,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.086,00</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,6%</t>
+          <t>R$ 5.918,00</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,4%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>1047</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,7%</t>
+        <v>1402</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,3%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7752,11 +7752,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7816,33 +7816,33 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.170,00</t>
+          <t>R$ 4.720,00</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>1099</v>
+        <v>1398</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,9%</t>
+          <t>▼ 9,3%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7898,11 +7898,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7932,78 +7932,1830 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 6.246,00</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>1541</v>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,9%</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>51,7%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 2.677,00</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,0%</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>1244</v>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,2%</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>40,7%</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.523,00</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 19,3%</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>1205</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,3%</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>45,5%</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 4.368,00</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,6%</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>1344</v>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,9%</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>50,7%</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.593,00</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>1319</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,8%</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>48,3%</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 4.791,00</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,8%</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>1308</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 1,4%</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>47,3%</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.663,00</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,8%</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>1326</v>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,3%</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>35,2%</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 2.959,00</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>1181</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>32,0%</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 2.959,00</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>1268</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,2%</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>34,4%</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 5.988,00</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>▲ 94,0%</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>2156</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>▲ 105,9%</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>56,8%</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.086,00</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>1047</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,7%</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>40,2%</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.170,00</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>UTD-092</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo Inox</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>3284176106</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>R$ 4.227,00</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I103" s="2" t="n">
+      <c r="I127" s="2" t="n">
         <v>1247</v>
       </c>
-      <c r="J103" s="2" t="inlineStr">
+      <c r="J127" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K103" s="2" t="inlineStr">
+      <c r="K127" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="L103" s="2" t="n">
+      <c r="L127" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="M103" s="2" t="inlineStr">
+      <c r="M127" s="2" t="inlineStr">
         <is>
           <t>45,9%</t>
         </is>
       </c>
-      <c r="N103" s="2" t="inlineStr">
+      <c r="N127" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
+++ b/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
+          <t>R$ 5.082,00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,8%</t>
+          <t>▲ 50,7%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>958</v>
+        <v>2029</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,3%</t>
+          <t>▲ 37,7%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,17 +738,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.228,00</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,0%</t>
+          <t>R$ 3.373,00</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▲ 5,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1001</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,4%</t>
+        <v>1474</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -894,20 +894,20 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.709,00</t>
+          <t>R$ 3.194,00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,8%</t>
+          <t>▲ 18,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>968</v>
+        <v>1228</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,8%</t>
+          <t>▼ 17,8%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1030,17 +1030,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,2%</t>
+          <t>R$ 2.705,00</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▲ 113,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>915</v>
+        <v>1494</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,2%</t>
+          <t>▲ 44,9%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 450,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.263,00</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+          <t>R$ 1.267,00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>976</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,5%</t>
+        <v>1031</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▲ 19,9%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1330,22 +1330,22 @@
       <c r="I12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 77,8%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.079,00</t>
+          <t>R$ 2.573,00</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>▲ 44,7%</t>
+          <t>▼ 13,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>943</v>
+        <v>860</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,1%</t>
+          <t>▼ 5,4%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1474,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 80,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
+          <t>R$ 2.983,00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,7%</t>
+          <t>▲ 39,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>864</v>
+        <v>909</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,4%</t>
+          <t>▲ 5,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1620,11 +1620,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.598,00</t>
+          <t>R$ 2.134,00</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>▼ 1,0%</t>
+          <t>▲ 15,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>885</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,4%</t>
+        <v>866</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,2%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.634,00</t>
+          <t>R$ 1.854,00</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,2%</t>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1085</v>
+        <v>1034</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,4%</t>
+          <t>▼ 0,8%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1912,11 +1912,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.486,00</t>
+          <t>R$ 2.448,00</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,9%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1001</v>
+        <v>1042</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,1%</t>
+          <t>▲ 11,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2058,11 +2058,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.524,00</t>
+          <t>R$ 1.632,00</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,7%</t>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1022</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 1,7%</t>
+        <v>939</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2204,11 +2204,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.450,00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,2%</t>
+          <t>R$ 3.560,00</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1040</v>
+        <v>1052</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,1%</t>
+          <t>▲ 2,5%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2350,11 +2350,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>10</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.599,00</t>
+          <t>R$ 3.634,00</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>▲ 21,4%</t>
+          <t>▼ 14,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1062</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,9%</t>
+        <v>1026</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3,3%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2496,11 +2496,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.787,00</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,7%</t>
+          <t>R$ 4.228,00</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>941</v>
+        <v>993</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,4%</t>
+          <t>▼ 11,8%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2636,17 +2636,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>8</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.239,00</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,7%</t>
+          <t>R$ 5.174,00</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,6%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>937</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>1126</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 12,2%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.497,00</t>
+          <t>R$ 5.785,00</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,6%</t>
+          <t>▼ 1,3%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1006</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1282</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 0,5%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2934,24 +2934,24 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
+          <t>R$ 5.859,00</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,7%</t>
+          <t>▲ 31,7%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
+        <v>1288</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 11,5%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3074,17 +3074,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.192,00</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,1%</t>
+          <t>R$ 4.450,00</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>854</v>
+        <v>1155</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,7%</t>
+          <t>▼ 10,3%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3230,20 +3230,20 @@
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,2%</t>
+          <t>R$ 4.376,00</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>▲ 37,2%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>848</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,7%</t>
+        <v>1287</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,8%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3366,17 +3366,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.115,00</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+          <t>R$ 3.189,00</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 29,5%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>834</v>
+        <v>1048</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,5%</t>
+          <t>▲ 6,1%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3518,24 +3518,24 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.895,00</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,9%</t>
+          <t>R$ 4.524,00</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>▲ 17,3%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>976</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,9%</t>
+        <v>988</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3,1%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3666,9 +3666,9 @@
       <c r="I44" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3733,20 +3733,20 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>▲ 36,9%</t>
+          <t>▼ 8,8%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>896</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,4%</t>
+        <v>958</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3810,11 +3810,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,33 +3874,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
+          <t>R$ 4.228,00</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,6%</t>
+          <t>▲ 14,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,7%</t>
+        <v>1001</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3,4%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3956,11 +3956,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,5%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4020,33 +4020,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,1%</t>
+          <t>R$ 3.709,00</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>▼ 3,8%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>903</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,5%</t>
+        <v>968</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▲ 5,8%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4102,11 +4102,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,25 +4166,25 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,5%</t>
+          <t>R$ 3.857,00</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>817</v>
+        <v>915</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,1%</t>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4242,17 +4242,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4315,22 +4315,22 @@
           <t>R$ 3.263,00</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 34,3%</t>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>770</v>
+        <v>976</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,3%</t>
+          <t>▲ 3,5%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4394,24 +4394,24 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4458,33 +4458,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.969,00</t>
+          <t>R$ 4.079,00</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,9%</t>
+          <t>▲ 44,7%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>979</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,6%</t>
+        <v>943</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▲ 9,1%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4540,11 +4540,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4604,33 +4604,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.637,00</t>
+          <t>R$ 2.818,00</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>▲ 68,9%</t>
+          <t>▼ 21,7%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>973</v>
+        <v>864</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,1%</t>
+          <t>▼ 2,4%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4688,9 +4688,9 @@
       <c r="I58" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,33 +4750,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+          <t>R$ 3.598,00</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 1,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>810</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,4%</t>
+        <v>885</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,4%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4832,11 +4832,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4896,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.592,00</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,5%</t>
+          <t>R$ 3.634,00</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>914</v>
+        <v>1085</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,5%</t>
+          <t>▲ 8,4%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4978,11 +4978,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5042,25 +5042,25 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.472,00</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,3%</t>
+          <t>R$ 3.486,00</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>▼ 22,9%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1057</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 1,7%</t>
+        <v>1001</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,1%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5124,11 +5124,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5188,33 +5188,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.629,00</t>
+          <t>R$ 4.524,00</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,6%</t>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1075</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,7%</t>
+        <v>1022</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 1,7%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5270,11 +5270,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5334,33 +5334,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.747,00</t>
+          <t>R$ 4.450,00</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>▲ 68,5%</t>
+          <t>▼ 3,2%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1116</v>
+        <v>1040</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,7%</t>
+          <t>▼ 2,1%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5410,17 +5410,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5480,33 +5480,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
+          <t>R$ 4.599,00</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>▼ 45,7%</t>
+          <t>▲ 21,4%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>973</v>
+        <v>1062</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 35,1%</t>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5562,24 +5562,24 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5626,33 +5626,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.186,00</t>
+          <t>R$ 3.787,00</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>▲ 45,7%</t>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27,9%</t>
+        <v>941</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▲ 0,4%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5708,11 +5708,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5772,33 +5772,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.560,00</t>
+          <t>R$ 4.239,00</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,3%</t>
+          <t>▼ 5,7%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1173</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,4%</t>
+        <v>937</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -5888,12 +5888,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5918,33 +5918,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.412,00</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,9%</t>
+          <t>R$ 4.497,00</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,6%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,4%</t>
+        <v>1006</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6002,7 +6002,7 @@
       <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
+      <c r="J76" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -6034,12 +6034,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6064,33 +6064,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 54,1%</t>
+          <t>R$ 3.857,00</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1165</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 47,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6146,11 +6146,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6210,33 +6210,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.304,00</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 117,9%</t>
+          <t>R$ 5.192,00</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>▲ 32,1%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>2206</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 101,1%</t>
+        <v>854</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▲ 0,7%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6292,11 +6292,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6356,33 +6356,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,7%</t>
+          <t>R$ 3.931,00</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▲ 26,2%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1097</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,0%</t>
+        <v>848</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6432,17 +6432,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6502,33 +6502,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.147,00</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,9%</t>
+          <t>R$ 3.115,00</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>930</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,1%</t>
+        <v>834</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,5%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6584,24 +6584,24 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6648,33 +6648,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.823,00</t>
+          <t>R$ 4.895,00</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,6%</t>
+          <t>▲ 26,9%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1070</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,8%</t>
+        <v>976</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▲ 8,9%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6730,11 +6730,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6764,12 +6764,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6794,38 +6794,38 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.469,00</t>
+          <t>R$ 3.857,00</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,4%</t>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1061</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,4%</t>
+        <v>896</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,4%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6876,11 +6876,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6940,33 +6940,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.708,00</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 0,9%</t>
+          <t>R$ 2.818,00</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1368</v>
+        <v>918</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,9%</t>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7022,11 +7022,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7056,12 +7056,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7086,33 +7086,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.742,00</t>
+          <t>R$ 3.338,00</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,5%</t>
+          <t>▼ 15,1%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1485</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,6%</t>
+        <v>903</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7168,11 +7168,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7232,33 +7232,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.241,00</t>
+          <t>R$ 3.931,00</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,1%</t>
+          <t>▲ 20,5%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1211</v>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,2%</t>
+        <v>817</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,1%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7308,17 +7308,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7378,33 +7378,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.072,00</t>
+          <t>R$ 3.263,00</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,1%</t>
+          <t>▼ 34,3%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1208</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 0,2%</t>
+        <v>770</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,3%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7460,24 +7460,24 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7524,33 +7524,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.650,00</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,4%</t>
+          <t>R$ 4.969,00</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>1211</v>
+        <v>979</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,6%</t>
+          <t>▲ 0,6%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7567,12 +7567,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7606,11 +7606,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7670,33 +7670,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.918,00</t>
-        </is>
-      </c>
-      <c r="H99" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,4%</t>
+          <t>R$ 5.637,00</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>▲ 68,9%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>1402</v>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,3%</t>
+        <v>973</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▲ 20,1%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7752,11 +7752,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7816,33 +7816,33 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.720,00</t>
-        </is>
-      </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,4%</t>
+          <t>R$ 3.338,00</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>1398</v>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,3%</t>
+        <v>810</v>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,4%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7898,11 +7898,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7932,12 +7932,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -7962,33 +7962,33 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.246,00</t>
-        </is>
-      </c>
-      <c r="H103" s="4" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+          <t>R$ 3.592,00</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3,5%</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>1541</v>
+        <v>914</v>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,9%</t>
+          <t>▼ 13,5%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8044,11 +8044,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>▼ 83,3%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8108,33 +8108,33 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.677,00</t>
-        </is>
-      </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,0%</t>
+          <t>R$ 3.472,00</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>1244</v>
+        <v>1057</v>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,2%</t>
+          <t>▼ 1,7%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8151,12 +8151,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8190,11 +8190,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8254,38 +8254,38 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.523,00</t>
-        </is>
-      </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 19,3%</t>
+          <t>R$ 3.629,00</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>▼ 23,6%</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>1205</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,3%</t>
+        <v>1075</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>▼ 3,7%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
@@ -8297,12 +8297,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8330,17 +8330,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8400,25 +8400,25 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.368,00</t>
-        </is>
-      </c>
-      <c r="H109" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,6%</t>
+          <t>R$ 4.747,00</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>▲ 68,5%</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1344</v>
-      </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,9%</t>
+        <v>1116</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,7%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8473,33 +8473,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I110" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
-        </is>
-      </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8546,33 +8546,33 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.593,00</t>
-        </is>
-      </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+          <t>R$ 2.818,00</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>▼ 45,7%</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>1319</v>
+        <v>973</v>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,8%</t>
+          <t>▼ 35,1%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8628,24 +8628,24 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8692,33 +8692,33 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.791,00</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>▲ 30,8%</t>
+          <t>R$ 5.186,00</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>▲ 45,7%</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1308</v>
+        <v>1500</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>▼ 1,4%</t>
+          <t>▲ 27,9%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8774,11 +8774,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8838,38 +8838,38 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.663,00</t>
-        </is>
-      </c>
-      <c r="H115" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,8%</t>
+          <t>R$ 3.560,00</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>1326</v>
+        <v>1173</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,3%</t>
+          <t>▼ 5,4%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8920,11 +8920,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8954,12 +8954,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -8984,38 +8984,38 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.959,00</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 3.412,00</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>1181</v>
+        <v>1240</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,9%</t>
+          <t>▲ 6,4%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
@@ -9027,12 +9027,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9066,11 +9066,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9130,33 +9130,33 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.959,00</t>
-        </is>
-      </c>
-      <c r="H119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+          <t>R$ 2.893,00</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>▼ 54,1%</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>1268</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,2%</t>
+        <v>1165</v>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>▼ 47,2%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9173,12 +9173,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9212,11 +9212,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9246,12 +9246,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9276,20 +9276,20 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.988,00</t>
-        </is>
-      </c>
-      <c r="H121" s="4" t="inlineStr">
-        <is>
-          <t>▲ 94,0%</t>
+          <t>R$ 6.304,00</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>▲ 117,9%</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>2156</v>
-      </c>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>▲ 105,9%</t>
+        <v>2206</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▲ 101,1%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9298,11 +9298,11 @@
         </is>
       </c>
       <c r="L121" s="2" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -9319,12 +9319,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9360,9 +9360,9 @@
       <c r="I122" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9422,33 +9422,33 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.086,00</t>
+          <t>R$ 2.893,00</t>
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,6%</t>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>1047</v>
+        <v>1097</v>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,7%</t>
+          <t>▲ 18,0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9504,11 +9504,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9568,33 +9568,33 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.170,00</t>
-        </is>
-      </c>
-      <c r="H125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+          <t>R$ 2.147,00</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>1099</v>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,9%</t>
+        <v>930</v>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,1%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9650,11 +9650,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9684,78 +9684,3144 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 2.823,00</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,6%</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>1070</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>▲ 0,8%</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>40,1%</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.469,00</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,4%</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>1061</v>
+      </c>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>▼ 22,4%</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>43,0%</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.708,00</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>▼ 0,9%</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,9%</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>47,2%</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.742,00</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>▲ 15,5%</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>1485</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,6%</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>49,5%</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.241,00</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,1%</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>▲ 0,2%</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>50,4%</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 5.072,00</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>▲ 9,1%</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>1208</v>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>▼ 0,2%</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>51,3%</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 4.650,00</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,6%</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>49,1%</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 5.918,00</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,4%</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>1402</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>▲ 0,3%</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>52,8%</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 4.720,00</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="inlineStr">
+        <is>
+          <t>▼ 24,4%</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>1398</v>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,3%</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>43,3%</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 6.246,00</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>1541</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>▲ 23,9%</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>51,7%</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 2.677,00</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>▼ 24,0%</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>1244</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3,2%</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>40,7%</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.523,00</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>▼ 19,3%</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>1205</v>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,3%</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>45,5%</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 4.368,00</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>▲ 21,6%</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>1344</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,9%</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>50,7%</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.593,00</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>1319</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▲ 0,8%</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>48,3%</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 4.791,00</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>▲ 30,8%</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>1308</v>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>▼ 1,4%</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>47,3%</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.663,00</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>▲ 23,8%</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>1326</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▲ 12,3%</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>35,2%</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 2.959,00</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>1181</v>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>32,0%</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 2.959,00</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>1268</v>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>▼ 41,2%</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>34,4%</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 5.988,00</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>▲ 94,0%</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>2156</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>▲ 105,9%</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>56,8%</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.086,00</t>
+        </is>
+      </c>
+      <c r="H165" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>1047</v>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>▼ 4,7%</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>40,2%</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.170,00</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>UTD-092</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo Inox</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>3284176106</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>R$ 4.227,00</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I127" s="2" t="n">
+      <c r="I169" s="2" t="n">
         <v>1247</v>
       </c>
-      <c r="J127" s="2" t="inlineStr">
+      <c r="J169" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K127" s="2" t="inlineStr">
+      <c r="K169" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="L127" s="2" t="n">
+      <c r="L169" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="M127" s="2" t="inlineStr">
+      <c r="M169" s="2" t="inlineStr">
         <is>
           <t>45,9%</t>
         </is>
       </c>
-      <c r="N127" s="2" t="inlineStr">
+      <c r="N169" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
+++ b/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,8 +597,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -607,39 +609,41 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -662,33 +666,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.082,00</t>
+          <t>R$ 2.967,00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,7%</t>
+          <t>▼ 41,6%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2029</v>
+        <v>1255</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▲ 37,7%</t>
+          <t>▼ 38,1%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -738,17 +742,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,14 +782,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -808,33 +812,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.373,00</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,6%</t>
+          <t>R$ 5.082,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1474</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>2029</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,7%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +855,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -881,33 +885,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +928,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -954,25 +958,25 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.194,00</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▲ 18,1%</t>
+          <t>R$ 3.373,00</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1228</v>
+        <v>1474</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▼ 17,8%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
@@ -980,7 +984,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +1001,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1027,33 +1031,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 27,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1074,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1100,33 +1104,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.705,00</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▲ 113,5%</t>
+          <t>R$ 3.194,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1494</v>
+        <v>1228</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▲ 44,9%</t>
+          <t>▼ 17,8%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1147,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1173,33 +1177,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▲ 450,0%</t>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1220,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1246,33 +1250,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.267,00</t>
+          <t>R$ 2.705,00</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,8%</t>
+          <t>▲ 113,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1031</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▲ 19,9%</t>
+        <v>1494</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 44,9%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1293,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1324,20 +1328,20 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▼ 77,8%</t>
+          <t>▲ 450,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
@@ -1345,7 +1349,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1366,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1392,33 +1396,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.573,00</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,7%</t>
+          <t>R$ 1.267,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>860</v>
+        <v>1031</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▼ 5,4%</t>
+          <t>▲ 19,9%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1439,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1465,7 +1469,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1474,24 +1478,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▲ 80,0%</t>
+          <t>▼ 77,8%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1512,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1538,33 +1542,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.983,00</t>
+          <t>R$ 2.573,00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>▲ 39,8%</t>
+          <t>▼ 13,7%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>909</v>
+        <v>860</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▲ 5,0%</t>
+          <t>▼ 5,4%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1585,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1620,11 +1624,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,14 +1658,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1684,33 +1688,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.134,00</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▲ 15,1%</t>
+          <t>R$ 2.983,00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 39,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>866</v>
+        <v>909</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,2%</t>
+          <t>▲ 5,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1731,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1766,11 +1770,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,14 +1804,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1830,33 +1834,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.854,00</t>
+          <t>R$ 2.134,00</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>▼ 24,3%</t>
+          <t>▲ 15,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1034</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 0,8%</t>
+        <v>866</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,2%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,14 +1877,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1912,11 +1916,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>4</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,14 +1950,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1976,33 +1980,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.448,00</t>
+          <t>R$ 1.854,00</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1042</v>
+        <v>1034</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,0%</t>
+          <t>▼ 0,8%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,14 +2023,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2058,11 +2062,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,14 +2096,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2122,33 +2126,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.632,00</t>
+          <t>R$ 2.448,00</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>▼ 54,2%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>939</v>
+        <v>1042</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,7%</t>
+          <t>▲ 11,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,14 +2169,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2204,11 +2208,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,14 +2242,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2268,33 +2272,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.560,00</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 2,0%</t>
+          <t>R$ 1.632,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1052</v>
+        <v>939</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▲ 2,5%</t>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2315,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2384,14 +2388,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2414,33 +2418,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.634,00</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,0%</t>
+          <t>R$ 3.560,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1026</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▲ 3,3%</t>
+        <v>1052</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,5%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2461,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2498,9 +2502,9 @@
       <c r="I28" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,14 +2534,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2560,33 +2564,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.228,00</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,3%</t>
+          <t>R$ 3.634,00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>993</v>
+        <v>1026</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,8%</t>
+          <t>▲ 3,3%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,14 +2607,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2636,17 +2640,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,14 +2680,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2706,33 +2710,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.174,00</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,6%</t>
+          <t>R$ 4.228,00</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,3%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1126</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▼ 12,2%</t>
+        <v>993</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,8%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,14 +2753,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2779,33 +2783,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,14 +2826,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2852,33 +2856,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.785,00</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 1,3%</t>
+          <t>R$ 5.174,00</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,6%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1282</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 0,5%</t>
+        <v>1126</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,2%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,14 +2899,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2930,20 +2934,20 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
@@ -2968,14 +2972,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2998,33 +3002,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.859,00</t>
+          <t>R$ 5.785,00</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>▲ 31,7%</t>
+          <t>▼ 1,3%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1288</v>
+        <v>1282</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,5%</t>
+          <t>▼ 0,5%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,14 +3045,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3071,33 +3075,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,14 +3118,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3144,33 +3148,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.450,00</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1,7%</t>
+          <t>R$ 5.859,00</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 31,7%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1155</v>
+        <v>1288</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,3%</t>
+          <t>▲ 11,5%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,14 +3191,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3217,33 +3221,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,14 +3264,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3290,25 +3294,25 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.376,00</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>▲ 37,2%</t>
+          <t>R$ 4.450,00</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1287</v>
+        <v>1155</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,8%</t>
+          <t>▼ 10,3%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
@@ -3316,7 +3320,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,14 +3337,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3363,7 +3367,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3372,24 +3376,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,14 +3410,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3436,33 +3440,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.189,00</t>
+          <t>R$ 4.376,00</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>▼ 29,5%</t>
+          <t>▲ 37,2%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1048</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▲ 6,1%</t>
+        <v>1287</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,8%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3483,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3520,9 +3524,9 @@
       <c r="I42" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3552,14 +3556,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3582,33 +3586,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.524,00</t>
+          <t>R$ 3.189,00</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>▲ 17,3%</t>
+          <t>▼ 29,5%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>988</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▲ 3,1%</t>
+        <v>1048</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,1%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,14 +3629,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3664,11 +3668,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,14 +3702,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3728,33 +3732,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
+          <t>R$ 4.524,00</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>▼ 8,8%</t>
+          <t>▲ 17,3%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>958</v>
+        <v>988</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>▼ 4,3%</t>
+          <t>▲ 3,1%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,14 +3775,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3810,11 +3814,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3844,14 +3848,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3874,33 +3878,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.228,00</t>
+          <t>R$ 3.857,00</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,0%</t>
+          <t>▼ 8,8%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1001</v>
+        <v>958</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>▲ 3,4%</t>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,14 +3921,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3956,9 +3960,9 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
         <is>
           <t>▲ 100,0%</t>
         </is>
@@ -3990,14 +3994,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4020,33 +4024,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.709,00</t>
+          <t>R$ 4.228,00</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>▼ 3,8%</t>
+          <t>▲ 14,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>968</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,8%</t>
+        <v>1001</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,4%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,14 +4067,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4102,11 +4106,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,14 +4140,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4166,33 +4170,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
+          <t>R$ 3.709,00</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>▲ 18,2%</t>
+          <t>▼ 3,8%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>915</v>
+        <v>968</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,2%</t>
+          <t>▲ 5,8%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,14 +4213,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4248,11 +4252,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4282,14 +4286,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4312,33 +4316,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.263,00</t>
+          <t>R$ 3.857,00</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>976</v>
+        <v>915</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>▲ 3,5%</t>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,14 +4359,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4394,11 +4398,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,14 +4432,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4458,33 +4462,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.079,00</t>
+          <t>R$ 3.263,00</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>▲ 44,7%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>943</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▲ 9,1%</t>
+        <v>976</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,5%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,14 +4505,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4540,11 +4544,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4574,14 +4578,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4604,33 +4608,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
+          <t>R$ 4.079,00</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>▼ 21,7%</t>
+          <t>▲ 44,7%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>864</v>
+        <v>943</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▼ 2,4%</t>
+          <t>▲ 9,1%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,14 +4651,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4686,11 +4690,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4720,14 +4724,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4750,33 +4754,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.598,00</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 1,0%</t>
+          <t>R$ 2.818,00</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,7%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>885</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,4%</t>
+        <v>864</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,4%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,14 +4797,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4832,11 +4836,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4866,14 +4870,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4896,33 +4900,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.634,00</t>
+          <t>R$ 3.598,00</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>▲ 4,2%</t>
+          <t>▼ 1,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1085</v>
+        <v>885</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>▲ 8,4%</t>
+          <t>▼ 18,4%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,14 +4943,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4978,11 +4982,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5012,14 +5016,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5042,33 +5046,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.486,00</t>
+          <t>R$ 3.634,00</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>▼ 22,9%</t>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1001</v>
+        <v>1085</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>▼ 2,1%</t>
+          <t>▲ 8,4%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,12 +5089,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5126,9 +5130,9 @@
       <c r="I64" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5158,14 +5162,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5188,33 +5192,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.524,00</t>
+          <t>R$ 3.486,00</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>▲ 1,7%</t>
+          <t>▼ 22,9%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1022</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 1,7%</t>
+        <v>1001</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,1%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,14 +5235,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5270,11 +5274,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5304,14 +5308,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5334,33 +5338,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.450,00</t>
+          <t>R$ 4.524,00</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>▼ 3,2%</t>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1040</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▼ 2,1%</t>
+        <v>1022</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 1,7%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,14 +5381,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5416,11 +5420,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>1</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5450,14 +5454,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5480,33 +5484,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.599,00</t>
+          <t>R$ 4.450,00</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>▲ 21,4%</t>
+          <t>▼ 3,2%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1062</v>
+        <v>1040</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▲ 12,9%</t>
+          <t>▼ 2,1%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,14 +5527,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5562,11 +5566,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5596,14 +5600,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5626,33 +5630,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.787,00</t>
+          <t>R$ 4.599,00</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,7%</t>
+          <t>▲ 21,4%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>941</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▲ 0,4%</t>
+        <v>1062</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,14 +5673,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5708,11 +5712,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5742,14 +5746,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5772,33 +5776,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.239,00</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 5,7%</t>
+          <t>R$ 3.787,00</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,9%</t>
+          <t>▲ 0,4%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,14 +5819,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5854,11 +5858,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5888,14 +5892,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5918,33 +5922,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.497,00</t>
+          <t>R$ 4.239,00</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,6%</t>
+          <t>▼ 5,7%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1006</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>937</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,14 +5965,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6000,11 +6004,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6034,14 +6038,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6064,33 +6068,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
+          <t>R$ 4.497,00</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,7%</t>
+          <t>▲ 16,6%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1006</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6107,14 +6111,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6146,11 +6150,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6180,14 +6184,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6210,33 +6214,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.192,00</t>
+          <t>R$ 3.857,00</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>▲ 32,1%</t>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>854</v>
+        <v>0</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>▲ 0,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6253,12 +6257,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6294,9 +6298,9 @@
       <c r="I80" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6326,14 +6330,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6356,33 +6360,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>▲ 26,2%</t>
+          <t>R$ 5.192,00</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,1%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>848</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1,7%</t>
+        <v>854</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,7%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6399,14 +6403,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6432,17 +6436,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6472,14 +6476,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6502,33 +6506,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.115,00</t>
+          <t>R$ 3.931,00</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▲ 26,2%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>834</v>
+        <v>848</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,5%</t>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6545,14 +6549,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6575,33 +6579,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6618,14 +6622,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6648,33 +6652,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.895,00</t>
+          <t>R$ 3.115,00</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,9%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>976</v>
+        <v>834</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>▲ 8,9%</t>
+          <t>▼ 14,5%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6691,14 +6695,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6721,7 +6725,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6730,24 +6734,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6764,14 +6768,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6794,33 +6798,33 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>▲ 36,9%</t>
+          <t>R$ 4.895,00</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,9%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>896</v>
+        <v>976</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>▼ 2,4%</t>
+          <t>▲ 8,9%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6837,14 +6841,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6876,11 +6880,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6910,14 +6914,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6940,33 +6944,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
+          <t>R$ 3.857,00</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,6%</t>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>918</v>
+        <v>896</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>▲ 1,7%</t>
+          <t>▼ 2,4%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6983,12 +6987,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7024,9 +7028,9 @@
       <c r="I90" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7056,14 +7060,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7086,33 +7090,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,1%</t>
+          <t>R$ 2.818,00</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>903</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▲ 10,5%</t>
+        <v>918</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7129,14 +7133,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7168,11 +7172,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▲ 166,7%</t>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7202,14 +7206,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7232,33 +7236,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
+          <t>R$ 3.338,00</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>▲ 20,5%</t>
+          <t>▼ 15,1%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>817</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▲ 6,1%</t>
+        <v>903</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7275,14 +7279,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7308,17 +7312,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7348,14 +7352,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7378,33 +7382,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.263,00</t>
+          <t>R$ 3.931,00</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>▼ 34,3%</t>
+          <t>▲ 20,5%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>770</v>
+        <v>817</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>▼ 21,3%</t>
+          <t>▲ 6,1%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7421,14 +7425,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7451,33 +7455,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7494,14 +7498,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7524,33 +7528,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.969,00</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,9%</t>
+          <t>R$ 3.263,00</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 34,3%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>979</v>
+        <v>770</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>▲ 0,6%</t>
+          <t>▼ 21,3%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7567,14 +7571,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7597,7 +7601,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7606,24 +7610,24 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7640,14 +7644,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7670,33 +7674,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.637,00</t>
+          <t>R$ 4.969,00</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>▲ 68,9%</t>
+          <t>▼ 11,9%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>973</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▲ 20,1%</t>
+        <v>979</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,6%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7713,14 +7717,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7752,11 +7756,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7786,14 +7790,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7816,33 +7820,33 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
+          <t>R$ 5.637,00</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,1%</t>
+          <t>▲ 68,9%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>810</v>
+        <v>973</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,4%</t>
+          <t>▲ 20,1%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7859,14 +7863,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7898,11 +7902,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7932,14 +7936,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7962,25 +7966,25 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.592,00</t>
+          <t>R$ 3.338,00</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>▲ 3,5%</t>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>914</v>
-      </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,5%</t>
+        <v>810</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,4%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
@@ -7988,7 +7992,7 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8005,14 +8009,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8044,11 +8048,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8078,14 +8082,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8108,33 +8112,33 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.472,00</t>
+          <t>R$ 3.592,00</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>▼ 4,3%</t>
+          <t>▲ 3,5%</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>1057</v>
-      </c>
-      <c r="J105" s="4" t="inlineStr">
-        <is>
-          <t>▼ 1,7%</t>
+        <v>914</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,5%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8151,14 +8155,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8190,11 +8194,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8224,14 +8228,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8254,33 +8258,33 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.629,00</t>
-        </is>
-      </c>
-      <c r="H107" s="4" t="inlineStr">
-        <is>
-          <t>▼ 23,6%</t>
+          <t>R$ 3.472,00</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>1075</v>
-      </c>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>▼ 3,7%</t>
+        <v>1057</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 1,7%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8297,14 +8301,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8336,9 +8340,9 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
         <is>
           <t>▲ 100,0%</t>
         </is>
@@ -8370,14 +8374,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8400,33 +8404,33 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.747,00</t>
+          <t>R$ 3.629,00</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>▲ 68,5%</t>
+          <t>▼ 23,6%</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1116</v>
+        <v>1075</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,7%</t>
+          <t>▼ 3,7%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8443,14 +8447,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8476,17 +8480,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8516,14 +8520,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8546,33 +8550,33 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
+          <t>R$ 4.747,00</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>▼ 45,7%</t>
+          <t>▲ 68,5%</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>973</v>
+        <v>1116</v>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>▼ 35,1%</t>
+          <t>▲ 14,7%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8589,14 +8593,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8619,33 +8623,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I112" s="2" t="n">
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8662,14 +8666,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8692,33 +8696,33 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.186,00</t>
+          <t>R$ 2.818,00</t>
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>▲ 45,7%</t>
+          <t>▼ 45,7%</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1500</v>
+        <v>973</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>▲ 27,9%</t>
+          <t>▼ 35,1%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8735,14 +8739,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8765,7 +8769,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -8774,11 +8778,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8787,11 +8791,11 @@
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8808,14 +8812,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8838,33 +8842,33 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.560,00</t>
-        </is>
-      </c>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>▲ 4,3%</t>
+          <t>R$ 5.186,00</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>▲ 45,7%</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>1173</v>
+        <v>1500</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>▼ 5,4%</t>
+          <t>▲ 27,9%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -8881,14 +8885,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8920,11 +8924,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8954,14 +8958,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8984,33 +8988,33 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.412,00</t>
-        </is>
-      </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>▲ 17,9%</t>
+          <t>R$ 3.560,00</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>1240</v>
+        <v>1173</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>▲ 6,4%</t>
+          <t>▼ 5,4%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9027,14 +9031,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9066,11 +9070,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9100,14 +9104,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9130,33 +9134,33 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
+          <t>R$ 3.412,00</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>▼ 54,1%</t>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>1165</v>
+        <v>1240</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>▼ 47,2%</t>
+          <t>▲ 6,4%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9173,14 +9177,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9212,11 +9216,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9246,14 +9250,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9276,33 +9280,33 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.304,00</t>
+          <t>R$ 2.893,00</t>
         </is>
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>▲ 117,9%</t>
+          <t>▼ 54,1%</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>2206</v>
+        <v>1165</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>▲ 101,1%</t>
+          <t>▼ 47,2%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -9319,14 +9323,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9358,11 +9362,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9392,14 +9396,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9422,33 +9426,33 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
-        </is>
-      </c>
-      <c r="H123" s="3" t="inlineStr">
-        <is>
-          <t>▲ 34,7%</t>
+          <t>R$ 6.304,00</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>▲ 117,9%</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>1097</v>
-      </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>▲ 18,0%</t>
+        <v>2206</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>▲ 101,1%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9465,12 +9469,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9508,7 +9512,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9538,14 +9542,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9568,33 +9572,33 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.147,00</t>
+          <t>R$ 2.893,00</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>930</v>
+        <v>1097</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,1%</t>
+          <t>▲ 18,0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9611,14 +9615,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9650,11 +9654,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9684,14 +9688,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9714,33 +9718,33 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.823,00</t>
-        </is>
-      </c>
-      <c r="H127" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,6%</t>
+          <t>R$ 2.147,00</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>1070</v>
+        <v>930</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>▲ 0,8%</t>
+          <t>▼ 13,1%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -9757,14 +9761,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9796,11 +9800,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J128" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9830,14 +9834,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9860,38 +9864,38 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.469,00</t>
-        </is>
-      </c>
-      <c r="H129" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,4%</t>
+          <t>R$ 2.823,00</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>1061</v>
+        <v>1070</v>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>▼ 22,4%</t>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
@@ -9903,14 +9907,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9942,11 +9946,11 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -9976,14 +9980,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10006,38 +10010,38 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.708,00</t>
-        </is>
-      </c>
-      <c r="H131" s="4" t="inlineStr">
-        <is>
-          <t>▼ 0,9%</t>
+          <t>R$ 3.469,00</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,4%</t>
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>1368</v>
-      </c>
-      <c r="J131" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,9%</t>
+        <v>1061</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,4%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L131" s="2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
@@ -10049,14 +10053,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10088,7 +10092,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -10122,14 +10126,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10152,33 +10156,33 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.742,00</t>
+          <t>R$ 3.708,00</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>▲ 15,5%</t>
+          <t>▼ 0,9%</t>
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>1485</v>
+        <v>1368</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,6%</t>
+          <t>▼ 7,9%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L133" s="2" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
@@ -10195,12 +10199,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10268,14 +10272,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10298,33 +10302,33 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.241,00</t>
+          <t>R$ 3.742,00</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,1%</t>
+          <t>▲ 15,5%</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>1211</v>
-      </c>
-      <c r="J135" s="3" t="inlineStr">
-        <is>
-          <t>▲ 0,2%</t>
+        <v>1485</v>
+      </c>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L135" s="2" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
@@ -10341,12 +10345,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10382,9 +10386,9 @@
       <c r="I136" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J136" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10414,14 +10418,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10444,33 +10448,33 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.072,00</t>
+          <t>R$ 3.241,00</t>
         </is>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>▲ 9,1%</t>
+          <t>▼ 36,1%</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>▼ 0,2%</t>
+          <t>▲ 0,2%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L137" s="2" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -10487,14 +10491,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10526,11 +10530,11 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10560,14 +10564,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10590,33 +10594,33 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.650,00</t>
+          <t>R$ 5.072,00</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>▼ 21,4%</t>
+          <t>▲ 9,1%</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>1211</v>
-      </c>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,6%</t>
+        <v>1208</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,2%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L139" s="2" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
@@ -10633,14 +10637,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10672,11 +10676,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10706,14 +10710,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10736,33 +10740,33 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.918,00</t>
+          <t>R$ 4.650,00</t>
         </is>
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,4%</t>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>1402</v>
+        <v>1211</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>▲ 0,3%</t>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L141" s="2" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -10779,14 +10783,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10818,11 +10822,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10852,14 +10856,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10882,33 +10886,33 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.720,00</t>
+          <t>R$ 5.918,00</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>▼ 24,4%</t>
+          <t>▲ 25,4%</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>▼ 9,3%</t>
+          <t>▲ 0,3%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L143" s="2" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -10925,14 +10929,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10964,11 +10968,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -10998,14 +11002,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11028,33 +11032,33 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.246,00</t>
+          <t>R$ 4.720,00</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>▲ 133,3%</t>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>1541</v>
+        <v>1398</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>▲ 23,9%</t>
+          <t>▼ 9,3%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L145" s="2" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -11071,14 +11075,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11110,11 +11114,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>▼ 83,3%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11144,14 +11148,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11174,33 +11178,33 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.677,00</t>
+          <t>R$ 6.246,00</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>▼ 24,0%</t>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>1244</v>
-      </c>
-      <c r="J147" s="3" t="inlineStr">
-        <is>
-          <t>▲ 3,2%</t>
+        <v>1541</v>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L147" s="2" t="n">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -11217,14 +11221,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11256,11 +11260,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11290,14 +11294,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11320,38 +11324,38 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.523,00</t>
-        </is>
-      </c>
-      <c r="H149" s="4" t="inlineStr">
-        <is>
-          <t>▼ 19,3%</t>
+          <t>R$ 2.677,00</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,0%</t>
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>1205</v>
+        <v>1244</v>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,3%</t>
+          <t>▲ 3,2%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L149" s="2" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
@@ -11363,14 +11367,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11396,17 +11400,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H150" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11436,14 +11440,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11466,38 +11470,38 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.368,00</t>
+          <t>R$ 3.523,00</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>▲ 21,6%</t>
+          <t>▼ 19,3%</t>
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>1344</v>
+        <v>1205</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>▲ 1,9%</t>
+          <t>▼ 10,3%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L151" s="2" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
@@ -11509,14 +11513,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11539,33 +11543,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11582,14 +11586,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11612,33 +11616,33 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.593,00</t>
+          <t>R$ 4.368,00</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>1319</v>
-      </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>▲ 0,8%</t>
+        <v>1344</v>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,9%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L153" s="2" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -11655,14 +11659,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11685,7 +11689,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -11694,24 +11698,24 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L154" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11728,14 +11732,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11758,33 +11762,33 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.791,00</t>
+          <t>R$ 3.593,00</t>
         </is>
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>▲ 30,8%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>1308</v>
+        <v>1319</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>▼ 1,4%</t>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L155" s="2" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -11801,14 +11805,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11840,11 +11844,11 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J156" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -11874,14 +11878,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11904,38 +11908,38 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.663,00</t>
-        </is>
-      </c>
-      <c r="H157" s="3" t="inlineStr">
-        <is>
-          <t>▲ 23,8%</t>
+          <t>R$ 4.791,00</t>
+        </is>
+      </c>
+      <c r="H157" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>1326</v>
+        <v>1308</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>▲ 12,3%</t>
+          <t>▼ 1,4%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
@@ -11947,14 +11951,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11986,11 +11990,11 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12020,14 +12024,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12050,33 +12054,33 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.959,00</t>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 3.663,00</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,8%</t>
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>1181</v>
+        <v>1326</v>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,9%</t>
+          <t>▲ 12,3%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L159" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -12093,14 +12097,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12132,11 +12136,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12166,14 +12170,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12199,35 +12203,35 @@
           <t>R$ 2.959,00</t>
         </is>
       </c>
-      <c r="H161" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>1268</v>
-      </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>▼ 41,2%</t>
+        <v>1181</v>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L161" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
@@ -12239,14 +12243,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12278,11 +12282,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12312,14 +12316,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12342,33 +12346,33 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.988,00</t>
+          <t>R$ 2.959,00</t>
         </is>
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>▲ 94,0%</t>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>2156</v>
+        <v>1268</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>▲ 105,9%</t>
+          <t>▼ 41,2%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L163" s="2" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -12385,12 +12389,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12426,9 +12430,9 @@
       <c r="I164" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12458,14 +12462,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12488,33 +12492,33 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.086,00</t>
+          <t>R$ 5.988,00</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>▼ 2,6%</t>
+          <t>▲ 94,0%</t>
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>1047</v>
+        <v>2156</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>▼ 4,7%</t>
+          <t>▲ 105,9%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L165" s="2" t="n">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -12531,14 +12535,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12570,11 +12574,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12604,14 +12608,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12634,20 +12638,20 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.170,00</t>
-        </is>
-      </c>
-      <c r="H167" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+          <t>R$ 3.086,00</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>1099</v>
-      </c>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,9%</t>
+        <v>1047</v>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,7%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12656,11 +12660,11 @@
         </is>
       </c>
       <c r="L167" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -12677,14 +12681,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12716,11 +12720,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12750,78 +12754,224 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.170,00</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>UTD-092</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo Inox</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>3284176106</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>R$ 4.227,00</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I169" s="2" t="n">
+      <c r="I171" s="2" t="n">
         <v>1247</v>
       </c>
-      <c r="J169" s="2" t="inlineStr">
+      <c r="J171" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K169" s="2" t="inlineStr">
+      <c r="K171" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="L169" s="2" t="n">
+      <c r="L171" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="M169" s="2" t="inlineStr">
+      <c r="M171" s="2" t="inlineStr">
         <is>
           <t>45,9%</t>
         </is>
       </c>
-      <c r="N169" s="2" t="inlineStr">
+      <c r="N171" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O169" s="2" t="inlineStr">
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
+++ b/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,14 +636,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -666,33 +666,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.967,00</t>
+          <t>R$ 2.373,00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,6%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1255</v>
+        <v>917</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 38,1%</t>
+          <t>▼ 26,9%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -739,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -747,8 +747,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -757,39 +759,41 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -812,33 +816,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.082,00</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,7%</t>
+          <t>R$ 2.967,00</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2029</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,7%</t>
+        <v>1255</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,1%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -855,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -888,17 +892,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -928,14 +932,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -958,33 +962,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.373,00</t>
+          <t>R$ 5.082,00</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,6%</t>
+          <t>▲ 50,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1474</v>
+        <v>2029</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▲ 37,7%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1001,14 +1005,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1031,33 +1035,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1074,14 +1078,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1104,25 +1108,25 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.194,00</t>
+          <t>R$ 3.373,00</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,1%</t>
+          <t>▲ 5,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1228</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,8%</t>
+        <v>1474</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
@@ -1130,7 +1134,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1147,14 +1151,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1177,33 +1181,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,3%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1220,14 +1224,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1250,33 +1254,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.705,00</t>
+          <t>R$ 3.194,00</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>▲ 113,5%</t>
+          <t>▲ 18,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1494</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 44,9%</t>
+        <v>1228</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,8%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1293,14 +1297,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1323,33 +1327,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 450,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1366,14 +1370,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1396,33 +1400,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.267,00</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,8%</t>
+          <t>R$ 2.705,00</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 113,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1031</v>
+        <v>1494</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▲ 19,9%</t>
+          <t>▲ 44,9%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1439,14 +1443,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1474,20 +1478,20 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 77,8%</t>
+        <v>11</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 450,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
@@ -1495,7 +1499,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1512,14 +1516,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1542,33 +1546,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.573,00</t>
+          <t>R$ 1.267,00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,7%</t>
+          <t>▼ 50,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>860</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,4%</t>
+        <v>1031</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 19,9%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1585,14 +1589,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1615,7 +1619,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1624,24 +1628,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 77,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1658,14 +1662,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1688,33 +1692,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.983,00</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 39,8%</t>
+          <t>R$ 2.573,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>909</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,0%</t>
+        <v>860</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,4%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1731,14 +1735,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1770,11 +1774,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 80,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1804,14 +1808,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1834,33 +1838,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.134,00</t>
+          <t>R$ 2.983,00</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,1%</t>
+          <t>▲ 39,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>866</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,2%</t>
+        <v>909</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1877,14 +1881,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1916,11 +1920,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1950,14 +1954,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1980,33 +1984,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.854,00</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,3%</t>
+          <t>R$ 2.134,00</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1034</v>
+        <v>866</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 0,8%</t>
+          <t>▼ 16,2%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2023,14 +2027,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2062,11 +2066,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2096,14 +2100,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2126,33 +2130,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.448,00</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 1.854,00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1042</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,0%</t>
+        <v>1034</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,8%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2169,14 +2173,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2208,11 +2212,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,0%</t>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2242,14 +2246,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2272,33 +2276,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.632,00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 54,2%</t>
+          <t>R$ 2.448,00</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>939</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,7%</t>
+        <v>1042</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2315,14 +2319,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2354,11 +2358,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2388,14 +2392,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2418,33 +2422,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.560,00</t>
+          <t>R$ 1.632,00</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,0%</t>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1052</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,5%</t>
+        <v>939</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2461,12 +2465,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2534,14 +2538,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2564,33 +2568,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.634,00</t>
+          <t>R$ 3.560,00</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,0%</t>
+          <t>▼ 2,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1026</v>
+        <v>1052</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,3%</t>
+          <t>▲ 2,5%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2607,12 +2611,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2648,9 +2652,9 @@
       <c r="I30" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2680,14 +2684,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2710,33 +2714,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.228,00</t>
+          <t>R$ 3.634,00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,3%</t>
+          <t>▼ 14,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>993</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,8%</t>
+        <v>1026</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,3%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2753,14 +2757,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2786,17 +2790,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2826,14 +2830,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2856,33 +2860,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.174,00</t>
+          <t>R$ 4.228,00</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,6%</t>
+          <t>▼ 18,3%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1126</v>
+        <v>993</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,2%</t>
+          <t>▼ 11,8%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2899,14 +2903,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2929,33 +2933,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2972,14 +2976,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3002,33 +3006,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.785,00</t>
+          <t>R$ 5.174,00</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>▼ 1,3%</t>
+          <t>▼ 10,6%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1282</v>
+        <v>1126</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 0,5%</t>
+          <t>▼ 12,2%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3045,14 +3049,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3080,20 +3084,20 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
@@ -3118,14 +3122,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3148,33 +3152,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.859,00</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 31,7%</t>
+          <t>R$ 5.785,00</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 1,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1288</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,5%</t>
+        <v>1282</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,5%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3191,14 +3195,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3221,33 +3225,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3264,14 +3268,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3294,33 +3298,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.450,00</t>
+          <t>R$ 5.859,00</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,7%</t>
+          <t>▲ 31,7%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1155</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,3%</t>
+        <v>1288</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,5%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3337,14 +3341,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3367,33 +3371,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3410,14 +3414,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3440,25 +3444,25 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.376,00</t>
+          <t>R$ 4.450,00</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,2%</t>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1287</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,8%</t>
+        <v>1155</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,3%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
@@ -3466,7 +3470,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3483,14 +3487,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3513,7 +3517,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3522,24 +3526,24 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3556,14 +3560,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3586,33 +3590,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.189,00</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 29,5%</t>
+          <t>R$ 4.376,00</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,2%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1048</v>
+        <v>1287</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,1%</t>
+          <t>▲ 22,8%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3629,12 +3633,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3670,9 +3674,9 @@
       <c r="I44" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3702,14 +3706,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3732,33 +3736,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.524,00</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,3%</t>
+          <t>R$ 3.189,00</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 29,5%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>988</v>
+        <v>1048</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,1%</t>
+          <t>▲ 6,1%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3775,14 +3779,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3814,11 +3818,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3848,14 +3852,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3878,33 +3882,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,8%</t>
+          <t>R$ 4.524,00</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,3%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>958</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,3%</t>
+        <v>988</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,1%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3921,14 +3925,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3960,11 +3964,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3994,14 +3998,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4024,33 +4028,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.228,00</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,0%</t>
+          <t>R$ 3.857,00</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,8%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1001</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,4%</t>
+        <v>958</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4067,14 +4071,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4106,7 +4110,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
@@ -4140,14 +4144,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4170,33 +4174,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.709,00</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,8%</t>
+          <t>R$ 4.228,00</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>968</v>
+        <v>1001</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,8%</t>
+          <t>▲ 3,4%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4213,14 +4217,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4252,11 +4256,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4286,14 +4290,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4316,33 +4320,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,2%</t>
+          <t>R$ 3.709,00</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,8%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>915</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,2%</t>
+        <v>968</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,8%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4359,14 +4363,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4398,11 +4402,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4432,14 +4436,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4462,33 +4466,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.263,00</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+          <t>R$ 3.857,00</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>976</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,5%</t>
+        <v>915</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4505,14 +4509,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4544,11 +4548,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4578,14 +4582,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4608,33 +4612,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.079,00</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 44,7%</t>
+          <t>R$ 3.263,00</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>943</v>
+        <v>976</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,1%</t>
+          <t>▲ 3,5%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4651,14 +4655,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4690,11 +4694,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4724,14 +4728,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4754,33 +4758,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,7%</t>
+          <t>R$ 4.079,00</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 44,7%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>864</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,4%</t>
+        <v>943</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,1%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4797,14 +4801,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4836,11 +4840,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4870,14 +4874,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4900,33 +4904,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.598,00</t>
+          <t>R$ 2.818,00</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>▼ 1,0%</t>
+          <t>▼ 21,7%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>885</v>
+        <v>864</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,4%</t>
+          <t>▼ 2,4%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4943,14 +4947,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4982,11 +4986,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5016,14 +5020,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5046,33 +5050,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.634,00</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,2%</t>
+          <t>R$ 3.598,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 1,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1085</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,4%</t>
+        <v>885</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,4%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5089,14 +5093,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5128,11 +5132,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5162,14 +5166,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5192,33 +5196,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.486,00</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,9%</t>
+          <t>R$ 3.634,00</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1001</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,1%</t>
+        <v>1085</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,4%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5235,12 +5239,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5276,9 +5280,9 @@
       <c r="I66" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5308,14 +5312,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5338,33 +5342,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.524,00</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,7%</t>
+          <t>R$ 3.486,00</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,9%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1022</v>
+        <v>1001</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▼ 1,7%</t>
+          <t>▼ 2,1%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5381,14 +5385,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5420,11 +5424,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5454,14 +5458,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5484,33 +5488,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.450,00</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,2%</t>
+          <t>R$ 4.524,00</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1040</v>
+        <v>1022</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,1%</t>
+          <t>▼ 1,7%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5527,14 +5531,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5566,11 +5570,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5600,14 +5604,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5630,33 +5634,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.599,00</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,4%</t>
+          <t>R$ 4.450,00</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,2%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1062</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,9%</t>
+        <v>1040</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,1%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5673,14 +5677,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5712,11 +5716,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5746,14 +5750,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5776,33 +5780,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.787,00</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,7%</t>
+          <t>R$ 4.599,00</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,4%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>941</v>
+        <v>1062</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,4%</t>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5819,14 +5823,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5858,11 +5862,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5892,14 +5896,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5922,33 +5926,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.239,00</t>
+          <t>R$ 3.787,00</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,7%</t>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>937</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>941</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,4%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5965,14 +5969,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6004,11 +6008,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6038,14 +6042,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6068,33 +6072,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.497,00</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,6%</t>
+          <t>R$ 4.239,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,7%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1006</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>937</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6111,14 +6115,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6150,11 +6154,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6184,14 +6188,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6214,33 +6218,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,7%</t>
+          <t>R$ 4.497,00</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,6%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1006</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6257,14 +6261,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6296,11 +6300,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6330,14 +6334,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6360,33 +6364,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.192,00</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,1%</t>
+          <t>R$ 3.857,00</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>854</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6403,12 +6407,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6444,9 +6448,9 @@
       <c r="I82" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6476,14 +6480,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6506,33 +6510,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
+          <t>R$ 5.192,00</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,2%</t>
+          <t>▲ 32,1%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,7%</t>
+          <t>▲ 0,7%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6549,14 +6553,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6582,17 +6586,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6622,14 +6626,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6652,33 +6656,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.115,00</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+          <t>R$ 3.931,00</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,2%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>834</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,5%</t>
+        <v>848</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6695,14 +6699,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6725,33 +6729,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6768,14 +6772,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6798,33 +6802,33 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.895,00</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,9%</t>
+          <t>R$ 3.115,00</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>976</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,9%</t>
+        <v>834</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,5%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6841,14 +6845,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6871,7 +6875,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6880,24 +6884,24 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6914,14 +6918,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6944,33 +6948,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
+          <t>R$ 4.895,00</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>▲ 36,9%</t>
+          <t>▲ 26,9%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>896</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,4%</t>
+        <v>976</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,9%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6987,14 +6991,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7026,11 +7030,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7060,14 +7064,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7090,33 +7094,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+          <t>R$ 3.857,00</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,7%</t>
+        <v>896</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,4%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7133,12 +7137,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7174,9 +7178,9 @@
       <c r="I92" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7206,14 +7210,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7236,33 +7240,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
+          <t>R$ 2.818,00</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,1%</t>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>903</v>
+        <v>918</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,5%</t>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7279,14 +7283,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7318,11 +7322,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7352,14 +7356,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7382,33 +7386,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,5%</t>
+          <t>R$ 3.338,00</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,1%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>817</v>
+        <v>903</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,1%</t>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7425,14 +7429,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7458,17 +7462,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7498,14 +7502,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7528,33 +7532,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.263,00</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 34,3%</t>
+          <t>R$ 3.931,00</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,5%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>770</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,3%</t>
+        <v>817</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,1%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7571,14 +7575,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7601,33 +7605,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7644,14 +7648,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7674,33 +7678,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.969,00</t>
+          <t>R$ 3.263,00</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,9%</t>
+          <t>▼ 34,3%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>979</v>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,6%</t>
+        <v>770</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,3%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7717,14 +7721,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7747,7 +7751,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7756,24 +7760,24 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7790,14 +7794,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7820,33 +7824,33 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.637,00</t>
-        </is>
-      </c>
-      <c r="H101" s="4" t="inlineStr">
-        <is>
-          <t>▲ 68,9%</t>
+          <t>R$ 4.969,00</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,1%</t>
+          <t>▲ 0,6%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7863,14 +7867,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7902,11 +7906,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7936,14 +7940,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7966,33 +7970,33 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
-        </is>
-      </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+          <t>R$ 5.637,00</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>▲ 68,9%</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>810</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,4%</t>
+        <v>973</v>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,1%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8009,14 +8013,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8048,11 +8052,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8082,14 +8086,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8112,25 +8116,25 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.592,00</t>
-        </is>
-      </c>
-      <c r="H105" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,5%</t>
+          <t>R$ 3.338,00</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>914</v>
+        <v>810</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,5%</t>
+          <t>▼ 11,4%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
@@ -8138,7 +8142,7 @@
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8155,14 +8159,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8194,11 +8198,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8228,14 +8232,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8258,33 +8262,33 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.472,00</t>
-        </is>
-      </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,3%</t>
+          <t>R$ 3.592,00</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,5%</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>1057</v>
+        <v>914</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>▼ 1,7%</t>
+          <t>▼ 13,5%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8301,14 +8305,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8340,11 +8344,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8374,14 +8378,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8404,33 +8408,33 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.629,00</t>
+          <t>R$ 3.472,00</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,6%</t>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1075</v>
+        <v>1057</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,7%</t>
+          <t>▼ 1,7%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8447,14 +8451,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8486,7 +8490,7 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
@@ -8520,14 +8524,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8550,33 +8554,33 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.747,00</t>
-        </is>
-      </c>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t>▲ 68,5%</t>
+          <t>R$ 3.629,00</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,6%</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>1116</v>
-      </c>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,7%</t>
+        <v>1075</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,7%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8593,14 +8597,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8626,17 +8630,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8666,14 +8670,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8696,33 +8700,33 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
-        </is>
-      </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 45,7%</t>
+          <t>R$ 4.747,00</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>▲ 68,5%</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>973</v>
-      </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,1%</t>
+        <v>1116</v>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,7%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8739,14 +8743,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8769,33 +8773,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I114" s="2" t="n">
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8812,14 +8816,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8842,33 +8846,33 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.186,00</t>
-        </is>
-      </c>
-      <c r="H115" s="4" t="inlineStr">
-        <is>
-          <t>▲ 45,7%</t>
+          <t>R$ 2.818,00</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 45,7%</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J115" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27,9%</t>
+        <v>973</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,1%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -8885,14 +8889,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8915,7 +8919,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -8924,11 +8928,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8937,11 +8941,11 @@
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -8958,14 +8962,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8988,33 +8992,33 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.560,00</t>
+          <t>R$ 5.186,00</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,3%</t>
+          <t>▲ 45,7%</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>1173</v>
-      </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,4%</t>
+        <v>1500</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27,9%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9031,14 +9035,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9070,11 +9074,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9104,14 +9108,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9134,33 +9138,33 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.412,00</t>
+          <t>R$ 3.560,00</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>▲ 17,9%</t>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,4%</t>
+        <v>1173</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,4%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9177,14 +9181,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9216,11 +9220,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9250,14 +9254,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9280,33 +9284,33 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
-        </is>
-      </c>
-      <c r="H121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 54,1%</t>
+          <t>R$ 3.412,00</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>1165</v>
-      </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 47,2%</t>
+        <v>1240</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,4%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -9323,14 +9327,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9362,11 +9366,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9396,14 +9400,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9426,33 +9430,33 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.304,00</t>
-        </is>
-      </c>
-      <c r="H123" s="4" t="inlineStr">
-        <is>
-          <t>▲ 117,9%</t>
+          <t>R$ 2.893,00</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 54,1%</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>2206</v>
-      </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>▲ 101,1%</t>
+        <v>1165</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,2%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9469,14 +9473,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9508,11 +9512,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9542,14 +9546,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9572,33 +9576,33 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
+          <t>R$ 6.304,00</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>▲ 34,7%</t>
+          <t>▲ 117,9%</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>1097</v>
+        <v>2206</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,0%</t>
+          <t>▲ 101,1%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9615,12 +9619,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9658,7 +9662,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9688,14 +9692,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9718,33 +9722,33 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.147,00</t>
-        </is>
-      </c>
-      <c r="H127" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,9%</t>
+          <t>R$ 2.893,00</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>930</v>
-      </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,1%</t>
+        <v>1097</v>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -9761,14 +9765,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9800,11 +9804,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9834,14 +9838,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9864,33 +9868,33 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.823,00</t>
+          <t>R$ 2.147,00</t>
         </is>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,6%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>1070</v>
-      </c>
-      <c r="J129" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,8%</t>
+        <v>930</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,1%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -9907,14 +9911,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9946,11 +9950,11 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -9980,14 +9984,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10010,38 +10014,38 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.469,00</t>
+          <t>R$ 2.823,00</t>
         </is>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,4%</t>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>1061</v>
-      </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,4%</t>
+        <v>1070</v>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L131" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
@@ -10053,14 +10057,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10092,11 +10096,11 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10126,14 +10130,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10156,38 +10160,38 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.708,00</t>
+          <t>R$ 3.469,00</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>▼ 0,9%</t>
+          <t>▼ 6,4%</t>
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>1368</v>
+        <v>1061</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,9%</t>
+          <t>▼ 22,4%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L133" s="2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
@@ -10199,14 +10203,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10238,7 +10242,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10272,14 +10276,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10302,33 +10306,33 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.742,00</t>
-        </is>
-      </c>
-      <c r="H135" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,5%</t>
+          <t>R$ 3.708,00</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,9%</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>1485</v>
-      </c>
-      <c r="J135" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,6%</t>
+        <v>1368</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,9%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L135" s="2" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
@@ -10345,12 +10349,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10418,14 +10422,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10448,33 +10452,33 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.241,00</t>
-        </is>
-      </c>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,1%</t>
+          <t>R$ 3.742,00</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,5%</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>1211</v>
+        <v>1485</v>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,2%</t>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L137" s="2" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -10491,12 +10495,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10532,9 +10536,9 @@
       <c r="I138" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10564,14 +10568,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10594,33 +10598,33 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.072,00</t>
-        </is>
-      </c>
-      <c r="H139" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,1%</t>
+          <t>R$ 3.241,00</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,1%</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>1208</v>
-      </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>▼ 0,2%</t>
+        <v>1211</v>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,2%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L139" s="2" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
@@ -10637,14 +10641,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10676,11 +10680,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10710,14 +10714,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10740,33 +10744,33 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.650,00</t>
-        </is>
-      </c>
-      <c r="H141" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,4%</t>
+          <t>R$ 5.072,00</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,1%</t>
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,6%</t>
+          <t>▼ 0,2%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L141" s="2" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -10783,14 +10787,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10822,11 +10826,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10856,14 +10860,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10886,33 +10890,33 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.918,00</t>
-        </is>
-      </c>
-      <c r="H143" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,4%</t>
+          <t>R$ 4.650,00</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>1402</v>
-      </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,3%</t>
+        <v>1211</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L143" s="2" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -10929,14 +10933,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10968,11 +10972,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11002,14 +11006,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11032,33 +11036,33 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.720,00</t>
-        </is>
-      </c>
-      <c r="H145" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,4%</t>
+          <t>R$ 5.918,00</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,4%</t>
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>1398</v>
-      </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,3%</t>
+        <v>1402</v>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,3%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L145" s="2" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -11075,14 +11079,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11114,11 +11118,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11148,14 +11152,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11178,33 +11182,33 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.246,00</t>
-        </is>
-      </c>
-      <c r="H147" s="4" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+          <t>R$ 4.720,00</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>1541</v>
-      </c>
-      <c r="J147" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,9%</t>
+        <v>1398</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,3%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L147" s="2" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -11221,14 +11225,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11260,11 +11264,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11294,14 +11298,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11324,33 +11328,33 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.677,00</t>
-        </is>
-      </c>
-      <c r="H149" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,0%</t>
+          <t>R$ 6.246,00</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>1244</v>
+        <v>1541</v>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,2%</t>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L149" s="2" t="n">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -11367,14 +11371,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11406,11 +11410,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11440,14 +11444,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11470,38 +11474,38 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.523,00</t>
+          <t>R$ 2.677,00</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>▼ 19,3%</t>
+          <t>▼ 24,0%</t>
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>1205</v>
-      </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,3%</t>
+        <v>1244</v>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,2%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L151" s="2" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
@@ -11513,14 +11517,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11546,17 +11550,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11586,14 +11590,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11616,38 +11620,38 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.368,00</t>
-        </is>
-      </c>
-      <c r="H153" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,6%</t>
+          <t>R$ 3.523,00</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 19,3%</t>
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>1344</v>
-      </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,9%</t>
+        <v>1205</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,3%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L153" s="2" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
@@ -11659,14 +11663,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11689,33 +11693,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11732,14 +11736,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11762,33 +11766,33 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.593,00</t>
-        </is>
-      </c>
-      <c r="H155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+          <t>R$ 4.368,00</t>
+        </is>
+      </c>
+      <c r="H155" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>1319</v>
+        <v>1344</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,8%</t>
+          <t>▲ 1,9%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L155" s="2" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -11805,14 +11809,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11835,7 +11839,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -11844,24 +11848,24 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L156" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -11878,14 +11882,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11908,33 +11912,33 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.791,00</t>
-        </is>
-      </c>
-      <c r="H157" s="4" t="inlineStr">
-        <is>
-          <t>▲ 30,8%</t>
+          <t>R$ 3.593,00</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>1308</v>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 1,4%</t>
+        <v>1319</v>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -11951,14 +11955,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11990,11 +11994,11 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J158" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12024,14 +12028,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12054,38 +12058,38 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.663,00</t>
+          <t>R$ 4.791,00</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,8%</t>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>1326</v>
-      </c>
-      <c r="J159" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,3%</t>
+        <v>1308</v>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>▼ 1,4%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L159" s="2" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
@@ -12097,14 +12101,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12136,11 +12140,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12170,14 +12174,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12200,33 +12204,33 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.959,00</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 3.663,00</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,8%</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>1181</v>
-      </c>
-      <c r="J161" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>1326</v>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,3%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L161" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
@@ -12243,14 +12247,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12282,11 +12286,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12316,14 +12320,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12349,35 +12353,35 @@
           <t>R$ 2.959,00</t>
         </is>
       </c>
-      <c r="H163" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>1268</v>
+        <v>1181</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,2%</t>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L163" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
@@ -12389,14 +12393,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12428,11 +12432,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12462,14 +12466,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12492,33 +12496,33 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.988,00</t>
-        </is>
-      </c>
-      <c r="H165" s="4" t="inlineStr">
-        <is>
-          <t>▲ 94,0%</t>
+          <t>R$ 2.959,00</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>2156</v>
-      </c>
-      <c r="J165" s="4" t="inlineStr">
-        <is>
-          <t>▲ 105,9%</t>
+        <v>1268</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,2%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L165" s="2" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -12535,12 +12539,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12576,9 +12580,9 @@
       <c r="I166" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12608,14 +12612,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12638,33 +12642,33 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.086,00</t>
-        </is>
-      </c>
-      <c r="H167" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,6%</t>
+          <t>R$ 5.988,00</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t>▲ 94,0%</t>
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>1047</v>
-      </c>
-      <c r="J167" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,7%</t>
+        <v>2156</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>▲ 105,9%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L167" s="2" t="n">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -12681,14 +12685,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12720,11 +12724,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12754,14 +12758,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12784,20 +12788,20 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.170,00</t>
+          <t>R$ 3.086,00</t>
         </is>
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>1099</v>
+        <v>1047</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,9%</t>
+          <t>▼ 4,7%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -12806,11 +12810,11 @@
         </is>
       </c>
       <c r="L169" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
@@ -12827,14 +12831,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12866,11 +12870,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -12900,78 +12904,224 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.170,00</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>UTD-092</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo Inox</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>3284176106</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>R$ 4.227,00</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I171" s="2" t="n">
+      <c r="I173" s="2" t="n">
         <v>1247</v>
       </c>
-      <c r="J171" s="2" t="inlineStr">
+      <c r="J173" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K171" s="2" t="inlineStr">
+      <c r="K173" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="L171" s="2" t="n">
+      <c r="L173" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="M171" s="2" t="inlineStr">
+      <c r="M173" s="2" t="inlineStr">
         <is>
           <t>45,9%</t>
         </is>
       </c>
-      <c r="N171" s="2" t="inlineStr">
+      <c r="N173" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
+++ b/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,14 +636,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -666,33 +666,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.373,00</t>
+          <t>R$ 2.818,00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 18,8%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>917</v>
+        <v>974</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,9%</t>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,14 +786,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -816,33 +816,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.967,00</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,6%</t>
+          <t>R$ 2.373,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1255</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 38,1%</t>
+        <v>917</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 26,9%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -889,7 +889,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -897,8 +897,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -907,39 +909,41 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -962,33 +966,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.082,00</t>
+          <t>R$ 2.967,00</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,7%</t>
+          <t>▼ 41,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2029</v>
+        <v>1255</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,7%</t>
+          <t>▼ 38,1%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1005,14 +1009,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1038,17 +1042,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1078,14 +1082,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1108,33 +1112,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.373,00</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,6%</t>
+          <t>R$ 5.082,00</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1474</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>2029</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▲ 37,7%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1151,14 +1155,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1181,33 +1185,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1224,14 +1228,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1254,25 +1258,25 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.194,00</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,1%</t>
+          <t>R$ 3.373,00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▲ 5,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1228</v>
+        <v>1474</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,8%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
@@ -1280,7 +1284,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1297,14 +1301,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1327,33 +1331,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1370,14 +1374,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1400,33 +1404,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.705,00</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 113,5%</t>
+          <t>R$ 3.194,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▲ 18,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1494</v>
+        <v>1228</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▲ 44,9%</t>
+          <t>▼ 17,8%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1443,14 +1447,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1473,33 +1477,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 450,0%</t>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1516,14 +1520,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1546,33 +1550,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.267,00</t>
+          <t>R$ 2.705,00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,8%</t>
+          <t>▲ 113,5%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1031</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 19,9%</t>
+        <v>1494</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▲ 44,9%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1589,14 +1593,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1624,20 +1628,20 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 77,8%</t>
+          <t>▲ 450,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
@@ -1645,7 +1649,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1662,14 +1666,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1692,33 +1696,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.573,00</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,7%</t>
+          <t>R$ 1.267,00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>860</v>
+        <v>1031</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,4%</t>
+          <t>▲ 19,9%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1735,14 +1739,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1765,7 +1769,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1774,24 +1778,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 80,0%</t>
+          <t>▼ 77,8%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1808,14 +1812,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1838,33 +1842,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.983,00</t>
+          <t>R$ 2.573,00</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>▲ 39,8%</t>
+          <t>▼ 13,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>909</v>
+        <v>860</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,0%</t>
+          <t>▼ 5,4%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1881,14 +1885,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1920,11 +1924,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 80,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1954,14 +1958,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -1984,33 +1988,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.134,00</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,1%</t>
+          <t>R$ 2.983,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▲ 39,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>866</v>
+        <v>909</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,2%</t>
+          <t>▲ 5,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2027,14 +2031,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2066,11 +2070,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2100,14 +2104,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2130,33 +2134,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.854,00</t>
+          <t>R$ 2.134,00</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,3%</t>
+          <t>▲ 15,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1034</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 0,8%</t>
+        <v>866</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,2%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2173,14 +2177,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2212,11 +2216,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>4</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2246,14 +2250,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2276,33 +2280,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.448,00</t>
+          <t>R$ 1.854,00</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1042</v>
+        <v>1034</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>▲ 11,0%</t>
+          <t>▼ 0,8%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2319,14 +2323,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2358,11 +2362,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2392,14 +2396,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2422,33 +2426,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.632,00</t>
+          <t>R$ 2.448,00</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>▼ 54,2%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>939</v>
+        <v>1042</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,7%</t>
+          <t>▲ 11,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2465,14 +2469,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2504,11 +2508,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2538,14 +2542,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2568,33 +2572,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.560,00</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,0%</t>
+          <t>R$ 1.632,00</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1052</v>
+        <v>939</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,5%</t>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2611,12 +2615,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2684,14 +2688,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2714,33 +2718,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.634,00</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,0%</t>
+          <t>R$ 3.560,00</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1026</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,3%</t>
+        <v>1052</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2,5%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2757,12 +2761,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2798,9 +2802,9 @@
       <c r="I32" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2830,14 +2834,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2860,33 +2864,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.228,00</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,3%</t>
+          <t>R$ 3.634,00</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>993</v>
+        <v>1026</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,8%</t>
+          <t>▲ 3,3%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2903,14 +2907,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -2936,17 +2940,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2976,14 +2980,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3006,33 +3010,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.174,00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,6%</t>
+          <t>R$ 4.228,00</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,3%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1126</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,2%</t>
+        <v>993</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,8%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3049,14 +3053,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3079,33 +3083,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3122,14 +3126,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3152,33 +3156,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.785,00</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 1,3%</t>
+          <t>R$ 5.174,00</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,6%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1282</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 0,5%</t>
+        <v>1126</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 12,2%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3195,14 +3199,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3230,20 +3234,20 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -3268,14 +3272,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3298,33 +3302,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.859,00</t>
+          <t>R$ 5.785,00</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>▲ 31,7%</t>
+          <t>▼ 1,3%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1288</v>
+        <v>1282</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>▲ 11,5%</t>
+          <t>▼ 0,5%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3341,14 +3345,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3371,33 +3375,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 73,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3414,14 +3418,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3444,33 +3448,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.450,00</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,7%</t>
+          <t>R$ 5.859,00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▲ 31,7%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1155</v>
+        <v>1288</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,3%</t>
+          <t>▲ 11,5%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3487,14 +3491,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3517,33 +3521,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3560,14 +3564,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3590,25 +3594,25 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.376,00</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,2%</t>
+          <t>R$ 4.450,00</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1287</v>
+        <v>1155</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,8%</t>
+          <t>▼ 10,3%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
@@ -3616,7 +3620,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3633,14 +3637,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3663,7 +3667,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3672,24 +3676,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3706,14 +3710,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3736,33 +3740,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.189,00</t>
+          <t>R$ 4.376,00</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>▼ 29,5%</t>
+          <t>▲ 37,2%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1048</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,1%</t>
+        <v>1287</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,8%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3779,12 +3783,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3820,9 +3824,9 @@
       <c r="I46" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3852,14 +3856,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3882,33 +3886,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.524,00</t>
+          <t>R$ 3.189,00</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>▲ 17,3%</t>
+          <t>▼ 29,5%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>988</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,1%</t>
+        <v>1048</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,1%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3925,14 +3929,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -3964,11 +3968,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3998,14 +4002,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4028,33 +4032,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
+          <t>R$ 4.524,00</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,8%</t>
+          <t>▲ 17,3%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>958</v>
+        <v>988</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,3%</t>
+          <t>▲ 3,1%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4071,14 +4075,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4110,11 +4114,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4144,14 +4148,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4174,33 +4178,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.228,00</t>
+          <t>R$ 3.857,00</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,0%</t>
+          <t>▼ 8,8%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1001</v>
+        <v>958</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,4%</t>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4217,14 +4221,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4256,9 +4260,9 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
         <is>
           <t>▲ 100,0%</t>
         </is>
@@ -4290,14 +4294,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4320,33 +4324,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.709,00</t>
+          <t>R$ 4.228,00</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,8%</t>
+          <t>▲ 14,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>968</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,8%</t>
+        <v>1001</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3,4%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4363,14 +4367,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4402,11 +4406,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4436,14 +4440,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4466,33 +4470,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
+          <t>R$ 3.709,00</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,2%</t>
+          <t>▼ 3,8%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>915</v>
+        <v>968</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,2%</t>
+          <t>▲ 5,8%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4509,14 +4513,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4548,11 +4552,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4582,14 +4586,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4612,33 +4616,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.263,00</t>
+          <t>R$ 3.857,00</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>976</v>
+        <v>915</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,5%</t>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4655,14 +4659,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4694,11 +4698,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4728,14 +4732,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4758,33 +4762,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.079,00</t>
+          <t>R$ 3.263,00</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>▲ 44,7%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>943</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,1%</t>
+        <v>976</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3,5%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4801,14 +4805,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4840,11 +4844,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4874,14 +4878,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4904,33 +4908,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
+          <t>R$ 4.079,00</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,7%</t>
+          <t>▲ 44,7%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>864</v>
+        <v>943</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,4%</t>
+          <t>▲ 9,1%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4947,14 +4951,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -4986,11 +4990,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5020,14 +5024,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5050,33 +5054,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.598,00</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 1,0%</t>
+          <t>R$ 2.818,00</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,7%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>885</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,4%</t>
+        <v>864</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,4%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5093,14 +5097,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5132,11 +5136,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5166,14 +5170,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5196,33 +5200,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.634,00</t>
+          <t>R$ 3.598,00</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,2%</t>
+          <t>▼ 1,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1085</v>
+        <v>885</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,4%</t>
+          <t>▼ 18,4%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5239,14 +5243,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5278,11 +5282,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5312,14 +5316,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5342,33 +5346,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.486,00</t>
+          <t>R$ 3.634,00</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,9%</t>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1001</v>
+        <v>1085</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,1%</t>
+          <t>▲ 8,4%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5385,12 +5389,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5426,9 +5430,9 @@
       <c r="I68" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5458,14 +5462,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5488,33 +5492,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.524,00</t>
+          <t>R$ 3.486,00</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,7%</t>
+          <t>▼ 22,9%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1022</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 1,7%</t>
+        <v>1001</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,1%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5531,14 +5535,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5570,11 +5574,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5604,14 +5608,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5634,33 +5638,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.450,00</t>
+          <t>R$ 4.524,00</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,2%</t>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1040</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,1%</t>
+        <v>1022</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 1,7%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5677,14 +5681,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5716,11 +5720,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>1</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5750,14 +5754,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5780,33 +5784,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.599,00</t>
+          <t>R$ 4.450,00</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>▲ 21,4%</t>
+          <t>▼ 3,2%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1062</v>
+        <v>1040</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,9%</t>
+          <t>▼ 2,1%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5823,14 +5827,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5862,11 +5866,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5896,14 +5900,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -5926,33 +5930,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.787,00</t>
+          <t>R$ 4.599,00</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,7%</t>
+          <t>▲ 21,4%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>941</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,4%</t>
+        <v>1062</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5969,14 +5973,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6008,11 +6012,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6042,14 +6046,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6072,33 +6076,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.239,00</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,7%</t>
+          <t>R$ 3.787,00</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,9%</t>
+          <t>▲ 0,4%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6115,14 +6119,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6154,11 +6158,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6188,14 +6192,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6218,33 +6222,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.497,00</t>
+          <t>R$ 4.239,00</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,6%</t>
+          <t>▼ 5,7%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1006</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>937</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6261,14 +6265,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6300,11 +6304,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6334,14 +6338,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6364,33 +6368,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
+          <t>R$ 4.497,00</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,7%</t>
+          <t>▲ 16,6%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1006</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6407,14 +6411,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6446,11 +6450,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6480,14 +6484,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6510,33 +6514,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.192,00</t>
+          <t>R$ 3.857,00</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>▲ 32,1%</t>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>854</v>
+        <v>0</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6553,12 +6557,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6594,9 +6598,9 @@
       <c r="I84" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6626,14 +6630,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6656,33 +6660,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
-        </is>
-      </c>
-      <c r="H85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,2%</t>
+          <t>R$ 5.192,00</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>▲ 32,1%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>848</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,7%</t>
+        <v>854</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▲ 0,7%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6699,14 +6703,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6732,17 +6736,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6772,14 +6776,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6802,33 +6806,33 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.115,00</t>
+          <t>R$ 3.931,00</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▲ 26,2%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>834</v>
+        <v>848</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,5%</t>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6845,14 +6849,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6875,33 +6879,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6918,14 +6922,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -6948,33 +6952,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.895,00</t>
+          <t>R$ 3.115,00</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,9%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>976</v>
+        <v>834</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,9%</t>
+          <t>▼ 14,5%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6991,14 +6995,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7021,7 +7025,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7030,24 +7034,24 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7064,14 +7068,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7094,33 +7098,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="inlineStr">
-        <is>
-          <t>▲ 36,9%</t>
+          <t>R$ 4.895,00</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>▲ 26,9%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>896</v>
+        <v>976</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,4%</t>
+          <t>▲ 8,9%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7137,14 +7141,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7176,11 +7180,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7210,14 +7214,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7240,33 +7244,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
+          <t>R$ 3.857,00</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,6%</t>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>918</v>
+        <v>896</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,7%</t>
+          <t>▼ 2,4%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7283,12 +7287,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7324,9 +7328,9 @@
       <c r="I94" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7356,14 +7360,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7386,33 +7390,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
-        </is>
-      </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,1%</t>
+          <t>R$ 2.818,00</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>903</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,5%</t>
+        <v>918</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7429,14 +7433,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7468,11 +7472,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>▲ 166,7%</t>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7502,14 +7506,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7532,33 +7536,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
+          <t>R$ 3.338,00</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,5%</t>
+          <t>▼ 15,1%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>817</v>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,1%</t>
+        <v>903</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7575,14 +7579,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7608,17 +7612,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7648,14 +7652,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7678,33 +7682,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.263,00</t>
+          <t>R$ 3.931,00</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>▼ 34,3%</t>
+          <t>▲ 20,5%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>770</v>
+        <v>817</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,3%</t>
+          <t>▲ 6,1%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7721,14 +7725,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7751,33 +7755,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7794,14 +7798,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7824,33 +7828,33 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.969,00</t>
-        </is>
-      </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,9%</t>
+          <t>R$ 3.263,00</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>▼ 34,3%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>979</v>
+        <v>770</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,6%</t>
+          <t>▼ 21,3%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7867,14 +7871,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7897,7 +7901,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -7906,24 +7910,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -7940,14 +7944,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -7970,33 +7974,33 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.637,00</t>
+          <t>R$ 4.969,00</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>▲ 68,9%</t>
+          <t>▼ 11,9%</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>973</v>
-      </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,1%</t>
+        <v>979</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▲ 0,6%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8013,14 +8017,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8052,11 +8056,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8086,14 +8090,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8116,33 +8120,33 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
+          <t>R$ 5.637,00</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,1%</t>
+          <t>▲ 68,9%</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>810</v>
+        <v>973</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,4%</t>
+          <t>▲ 20,1%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8159,14 +8163,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8198,11 +8202,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8232,14 +8236,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8262,25 +8266,25 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.592,00</t>
+          <t>R$ 3.338,00</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,5%</t>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>914</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,5%</t>
+        <v>810</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,4%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
@@ -8288,7 +8292,7 @@
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8305,14 +8309,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8344,11 +8348,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8378,14 +8382,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8408,33 +8412,33 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.472,00</t>
+          <t>R$ 3.592,00</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,3%</t>
+          <t>▲ 3,5%</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1057</v>
-      </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 1,7%</t>
+        <v>914</v>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,5%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8451,14 +8455,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8490,11 +8494,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8524,14 +8528,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8554,33 +8558,33 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.629,00</t>
-        </is>
-      </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,6%</t>
+          <t>R$ 3.472,00</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>1075</v>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,7%</t>
+        <v>1057</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>▼ 1,7%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8597,14 +8601,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8636,9 +8640,9 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J112" s="4" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
         <is>
           <t>▲ 100,0%</t>
         </is>
@@ -8670,14 +8674,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8700,33 +8704,33 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.747,00</t>
+          <t>R$ 3.629,00</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>▲ 68,5%</t>
+          <t>▼ 23,6%</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1116</v>
+        <v>1075</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,7%</t>
+          <t>▼ 3,7%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8743,14 +8747,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8776,17 +8780,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8816,14 +8820,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8846,33 +8850,33 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
+          <t>R$ 4.747,00</t>
         </is>
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>▼ 45,7%</t>
+          <t>▲ 68,5%</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>973</v>
+        <v>1116</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>▼ 35,1%</t>
+          <t>▲ 14,7%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -8889,14 +8893,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8919,33 +8923,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I116" s="2" t="n">
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -8962,14 +8966,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -8992,33 +8996,33 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.186,00</t>
+          <t>R$ 2.818,00</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>▲ 45,7%</t>
+          <t>▼ 45,7%</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>1500</v>
+        <v>973</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>▲ 27,9%</t>
+          <t>▼ 35,1%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9035,14 +9039,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9065,7 +9069,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -9074,11 +9078,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9087,11 +9091,11 @@
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9108,14 +9112,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9138,33 +9142,33 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.560,00</t>
-        </is>
-      </c>
-      <c r="H119" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,3%</t>
+          <t>R$ 5.186,00</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>▲ 45,7%</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>1173</v>
+        <v>1500</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,4%</t>
+          <t>▲ 27,9%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9181,14 +9185,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9220,11 +9224,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9254,14 +9258,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9284,33 +9288,33 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.412,00</t>
-        </is>
-      </c>
-      <c r="H121" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,9%</t>
+          <t>R$ 3.560,00</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>1240</v>
+        <v>1173</v>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,4%</t>
+          <t>▼ 5,4%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -9327,14 +9331,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9366,11 +9370,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9400,14 +9404,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9430,33 +9434,33 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
+          <t>R$ 3.412,00</t>
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
-          <t>▼ 54,1%</t>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>1165</v>
+        <v>1240</v>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>▼ 47,2%</t>
+          <t>▲ 6,4%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9473,14 +9477,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9512,11 +9516,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9546,14 +9550,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9576,33 +9580,33 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.304,00</t>
+          <t>R$ 2.893,00</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>▲ 117,9%</t>
+          <t>▼ 54,1%</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>2206</v>
+        <v>1165</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>▲ 101,1%</t>
+          <t>▼ 47,2%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9619,14 +9623,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9658,11 +9662,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9692,14 +9696,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9722,33 +9726,33 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
-        </is>
-      </c>
-      <c r="H127" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,7%</t>
+          <t>R$ 6.304,00</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>▲ 117,9%</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>1097</v>
-      </c>
-      <c r="J127" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,0%</t>
+        <v>2206</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>▲ 101,1%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -9765,12 +9769,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -9808,7 +9812,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9838,14 +9842,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9868,33 +9872,33 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.147,00</t>
+          <t>R$ 2.893,00</t>
         </is>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>930</v>
+        <v>1097</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,1%</t>
+          <t>▲ 18,0%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -9911,14 +9915,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -9950,11 +9954,11 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -9984,14 +9988,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10014,33 +10018,33 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.823,00</t>
-        </is>
-      </c>
-      <c r="H131" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,6%</t>
+          <t>R$ 2.147,00</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>1070</v>
+        <v>930</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,8%</t>
+          <t>▼ 13,1%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L131" s="2" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -10057,14 +10061,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10096,11 +10100,11 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10130,14 +10134,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10160,38 +10164,38 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.469,00</t>
-        </is>
-      </c>
-      <c r="H133" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,4%</t>
+          <t>R$ 2.823,00</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>1061</v>
+        <v>1070</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,4%</t>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L133" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
@@ -10203,14 +10207,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10242,11 +10246,11 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10276,14 +10280,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10306,38 +10310,38 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.708,00</t>
-        </is>
-      </c>
-      <c r="H135" s="3" t="inlineStr">
-        <is>
-          <t>▼ 0,9%</t>
+          <t>R$ 3.469,00</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,4%</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>1368</v>
-      </c>
-      <c r="J135" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,9%</t>
+        <v>1061</v>
+      </c>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>▼ 22,4%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L135" s="2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
@@ -10349,14 +10353,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10388,7 +10392,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
@@ -10422,14 +10426,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10452,33 +10456,33 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.742,00</t>
+          <t>R$ 3.708,00</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,5%</t>
+          <t>▼ 0,9%</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>1485</v>
+        <v>1368</v>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,6%</t>
+          <t>▼ 7,9%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L137" s="2" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -10495,12 +10499,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10568,14 +10572,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10598,33 +10602,33 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.241,00</t>
+          <t>R$ 3.742,00</t>
         </is>
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,1%</t>
+          <t>▲ 15,5%</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>1211</v>
-      </c>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,2%</t>
+        <v>1485</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L139" s="2" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
@@ -10641,12 +10645,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10682,9 +10686,9 @@
       <c r="I140" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10714,14 +10718,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10744,33 +10748,33 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.072,00</t>
+          <t>R$ 3.241,00</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,1%</t>
+          <t>▼ 36,1%</t>
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>▼ 0,2%</t>
+          <t>▲ 0,2%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L141" s="2" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -10787,14 +10791,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10826,11 +10830,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10860,14 +10864,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10890,33 +10894,33 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.650,00</t>
+          <t>R$ 5.072,00</t>
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,4%</t>
+          <t>▲ 9,1%</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>1211</v>
-      </c>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,6%</t>
+        <v>1208</v>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>▼ 0,2%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L143" s="2" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -10933,14 +10937,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -10972,11 +10976,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11006,14 +11010,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11036,33 +11040,33 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.918,00</t>
+          <t>R$ 4.650,00</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,4%</t>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>1402</v>
+        <v>1211</v>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>▲ 0,3%</t>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L145" s="2" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -11079,14 +11083,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11118,11 +11122,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11152,14 +11156,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11182,33 +11186,33 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.720,00</t>
+          <t>R$ 5.918,00</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,4%</t>
+          <t>▲ 25,4%</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,3%</t>
+          <t>▲ 0,3%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L147" s="2" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -11225,14 +11229,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11264,11 +11268,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11298,14 +11302,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11328,33 +11332,33 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.246,00</t>
+          <t>R$ 4.720,00</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>▲ 133,3%</t>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>1541</v>
+        <v>1398</v>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,9%</t>
+          <t>▼ 9,3%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L149" s="2" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -11371,14 +11375,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11410,11 +11414,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>▼ 83,3%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11444,14 +11448,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11474,33 +11478,33 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.677,00</t>
+          <t>R$ 6.246,00</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,0%</t>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>1244</v>
-      </c>
-      <c r="J151" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,2%</t>
+        <v>1541</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L151" s="2" t="n">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -11517,14 +11521,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11556,11 +11560,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11590,14 +11594,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11620,38 +11624,38 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.523,00</t>
-        </is>
-      </c>
-      <c r="H153" s="3" t="inlineStr">
-        <is>
-          <t>▼ 19,3%</t>
+          <t>R$ 2.677,00</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>▼ 24,0%</t>
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>1205</v>
+        <v>1244</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,3%</t>
+          <t>▲ 3,2%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L153" s="2" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
@@ -11663,14 +11667,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11696,17 +11700,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11736,14 +11740,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11766,38 +11770,38 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.368,00</t>
+          <t>R$ 3.523,00</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>▲ 21,6%</t>
+          <t>▼ 19,3%</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>1344</v>
+        <v>1205</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,9%</t>
+          <t>▼ 10,3%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L155" s="2" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
@@ -11809,14 +11813,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11839,33 +11843,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -11882,14 +11886,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11912,33 +11916,33 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.593,00</t>
+          <t>R$ 4.368,00</t>
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>1319</v>
-      </c>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>▲ 0,8%</t>
+        <v>1344</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,9%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -11955,14 +11959,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -11985,7 +11989,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -11994,24 +11998,24 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L158" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12028,14 +12032,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12058,33 +12062,33 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.791,00</t>
+          <t>R$ 3.593,00</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>▲ 30,8%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>1308</v>
+        <v>1319</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>▼ 1,4%</t>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L159" s="2" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -12101,14 +12105,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12140,11 +12144,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12174,14 +12178,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12204,38 +12208,38 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.663,00</t>
-        </is>
-      </c>
-      <c r="H161" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,8%</t>
+          <t>R$ 4.791,00</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>1326</v>
+        <v>1308</v>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,3%</t>
+          <t>▼ 1,4%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L161" s="2" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
@@ -12247,14 +12251,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12286,11 +12290,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12320,14 +12324,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12350,33 +12354,33 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.959,00</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 3.663,00</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>▲ 23,8%</t>
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>1181</v>
+        <v>1326</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,9%</t>
+          <t>▲ 12,3%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L163" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -12393,14 +12397,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12432,11 +12436,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12466,14 +12470,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12499,35 +12503,35 @@
           <t>R$ 2.959,00</t>
         </is>
       </c>
-      <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>1268</v>
-      </c>
-      <c r="J165" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,2%</t>
+        <v>1181</v>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L165" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O165" s="2" t="inlineStr">
@@ -12539,14 +12543,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12578,11 +12582,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J166" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12612,14 +12616,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12642,33 +12646,33 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.988,00</t>
+          <t>R$ 2.959,00</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>▲ 94,0%</t>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>2156</v>
+        <v>1268</v>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>▲ 105,9%</t>
+          <t>▼ 41,2%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L167" s="2" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -12685,12 +12689,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -12726,9 +12730,9 @@
       <c r="I168" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12758,14 +12762,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12788,33 +12792,33 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.086,00</t>
+          <t>R$ 5.988,00</t>
         </is>
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,6%</t>
+          <t>▲ 94,0%</t>
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>1047</v>
+        <v>2156</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,7%</t>
+          <t>▲ 105,9%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L169" s="2" t="n">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
@@ -12831,14 +12835,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12870,11 +12874,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -12904,14 +12908,14 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -12934,20 +12938,20 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.170,00</t>
-        </is>
-      </c>
-      <c r="H171" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+          <t>R$ 3.086,00</t>
+        </is>
+      </c>
+      <c r="H171" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>1099</v>
-      </c>
-      <c r="J171" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,9%</t>
+        <v>1047</v>
+      </c>
+      <c r="J171" s="4" t="inlineStr">
+        <is>
+          <t>▼ 4,7%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -12956,11 +12960,11 @@
         </is>
       </c>
       <c r="L171" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
@@ -12977,14 +12981,14 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>UTD-092</t>
@@ -13016,11 +13020,11 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13050,78 +13054,224 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.170,00</t>
+        </is>
+      </c>
+      <c r="H173" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="J173" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>UTD-092</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo Inox</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>3284176106</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>R$ 4.227,00</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I173" s="2" t="n">
+      <c r="I175" s="2" t="n">
         <v>1247</v>
       </c>
-      <c r="J173" s="2" t="inlineStr">
+      <c r="J175" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K173" s="2" t="inlineStr">
+      <c r="K175" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="L173" s="2" t="n">
+      <c r="L175" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="M173" s="2" t="inlineStr">
+      <c r="M175" s="2" t="inlineStr">
         <is>
           <t>45,9%</t>
         </is>
       </c>
-      <c r="N173" s="2" t="inlineStr">
+      <c r="N175" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
+++ b/saida_skus/SKU_UTD-092-ESCORREDOR-DUPLO-INOX.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,59 +589,55 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -666,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▲ 18,8%</t>
+          <t>R$ 2.522,00</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,4%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>974</v>
+        <v>1031</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▲ 6,2%</t>
+          <t>▼ 17,7%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -709,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,59 +735,55 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -816,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.373,00</t>
+          <t>R$ 2.077,00</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>917</v>
+        <v>1252</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▼ 26,9%</t>
+          <t>▲ 21,4%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -859,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -889,59 +881,55 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -966,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.967,00</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>▼ 41,6%</t>
+          <t>R$ 1.187,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1255</v>
+        <v>1031</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▼ 38,1%</t>
+          <t>▲ 3,3%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1009,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1048,7 +1036,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1082,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1112,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.082,00</t>
+          <t>R$ 2.151,00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,7%</t>
+          <t>▼ 23,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2029</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▲ 37,7%</t>
+        <v>998</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,5%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1155,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1185,55 +1173,59 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1258,33 +1250,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.373,00</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,6%</t>
+          <t>R$ 2.818,00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1474</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>974</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1301,12 +1293,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1331,7 +1323,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1339,47 +1331,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1404,33 +1400,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.194,00</t>
+          <t>R$ 2.373,00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>▲ 18,1%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1228</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 17,8%</t>
+        <v>917</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,9%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1447,12 +1443,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1477,55 +1473,59 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 27,3%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1550,25 +1550,25 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.705,00</t>
+          <t>R$ 2.967,00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>▲ 113,5%</t>
+          <t>▼ 41,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1494</v>
+        <v>1255</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▲ 44,9%</t>
+          <t>▼ 38,1%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1593,12 +1593,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1623,33 +1623,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▲ 450,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1696,33 +1696,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.267,00</t>
+          <t>R$ 5.082,00</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,8%</t>
+          <t>▲ 50,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1031</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▲ 19,9%</t>
+        <v>2029</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,7%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1739,12 +1739,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1769,33 +1769,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 77,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1842,33 +1842,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.573,00</t>
+          <t>R$ 3.373,00</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,7%</t>
+          <t>▲ 5,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>860</v>
+        <v>1474</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▼ 5,4%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1924,24 +1924,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▲ 80,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1988,33 +1988,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.983,00</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▲ 39,8%</t>
+          <t>R$ 3.194,00</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>909</v>
+        <v>1228</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▲ 5,0%</t>
+          <t>▼ 17,8%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2064,17 +2064,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2134,33 +2134,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.134,00</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▲ 15,1%</t>
+          <t>R$ 2.705,00</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 113,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>866</v>
+        <v>1494</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,2%</t>
+          <t>▲ 44,9%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2207,33 +2207,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 450,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2280,33 +2280,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.854,00</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,3%</t>
+          <t>R$ 1.267,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>▼ 0,8%</t>
+          <t>▲ 19,9%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2323,12 +2323,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2362,24 +2362,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>2</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 77,8%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2426,33 +2426,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.448,00</t>
+          <t>R$ 2.573,00</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 13,7%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1042</v>
+        <v>860</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,0%</t>
+          <t>▼ 5,4%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,0%</t>
+          <t>▲ 80,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2542,12 +2542,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2572,33 +2572,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.632,00</t>
+          <t>R$ 2.983,00</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>▼ 54,2%</t>
+          <t>▲ 39,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>939</v>
+        <v>909</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,7%</t>
+          <t>▲ 5,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2615,12 +2615,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2654,11 +2654,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2688,12 +2688,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2718,33 +2718,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.560,00</t>
+          <t>R$ 2.134,00</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>▼ 2,0%</t>
+          <t>▲ 15,1%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1052</v>
+        <v>866</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▲ 2,5%</t>
+          <t>▼ 16,2%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2761,12 +2761,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2800,11 +2800,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2834,12 +2834,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2864,33 +2864,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.634,00</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,0%</t>
+          <t>R$ 1.854,00</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1026</v>
+        <v>1034</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▲ 3,3%</t>
+          <t>▼ 0,8%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2946,11 +2946,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2980,12 +2980,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3010,33 +3010,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.228,00</t>
+          <t>R$ 2.448,00</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>▼ 18,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>993</v>
+        <v>1042</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,8%</t>
+          <t>▲ 11,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3086,17 +3086,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3126,12 +3126,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3156,33 +3156,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.174,00</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,6%</t>
+          <t>R$ 1.632,00</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1126</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▼ 12,2%</t>
+        <v>939</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3199,12 +3199,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3229,33 +3229,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3302,33 +3302,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.785,00</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>▼ 1,3%</t>
+          <t>R$ 3.560,00</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1282</v>
+        <v>1052</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>▼ 0,5%</t>
+          <t>▲ 2,5%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3345,12 +3345,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3393,15 +3393,15 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3448,33 +3448,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.859,00</t>
+          <t>R$ 3.634,00</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>▲ 31,7%</t>
+          <t>▼ 14,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1288</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▲ 11,5%</t>
+        <v>1026</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,3%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3524,17 +3524,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3594,33 +3594,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.450,00</t>
+          <t>R$ 4.228,00</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>▲ 1,7%</t>
+          <t>▼ 18,3%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1155</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,3%</t>
+        <v>993</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,8%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3667,33 +3667,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3740,33 +3740,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.376,00</t>
+          <t>R$ 5.174,00</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>▲ 37,2%</t>
+          <t>▼ 10,6%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1287</v>
+        <v>1126</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,8%</t>
+          <t>▼ 12,2%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3783,12 +3783,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3813,33 +3813,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3886,33 +3886,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.189,00</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>▼ 29,5%</t>
+          <t>R$ 5.785,00</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 1,3%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1048</v>
+        <v>1282</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>▲ 6,1%</t>
+          <t>▼ 0,5%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3968,24 +3968,24 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4032,33 +4032,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.524,00</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>▲ 17,3%</t>
+          <t>R$ 5.859,00</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 31,7%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>988</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▲ 3,1%</t>
+        <v>1288</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,5%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4108,17 +4108,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4148,12 +4148,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4178,33 +4178,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
+          <t>R$ 4.450,00</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>▼ 8,8%</t>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>958</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,3%</t>
+        <v>1155</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,3%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4264,20 +4264,20 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4324,25 +4324,25 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.228,00</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>▲ 14,0%</t>
+          <t>R$ 4.376,00</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,2%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1001</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▲ 3,4%</t>
+        <v>1287</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,8%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4406,11 +4406,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4470,33 +4470,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.709,00</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>▼ 3,8%</t>
+          <t>R$ 3.189,00</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 29,5%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>968</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,8%</t>
+        <v>1048</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,1%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4552,11 +4552,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4586,12 +4586,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4616,33 +4616,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>▲ 18,2%</t>
+          <t>R$ 4.524,00</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,3%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>915</v>
+        <v>988</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,2%</t>
+          <t>▲ 3,1%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4698,11 +4698,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4762,33 +4762,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.263,00</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+          <t>R$ 3.857,00</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,8%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>976</v>
+        <v>958</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▲ 3,5%</t>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4805,12 +4805,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4844,11 +4844,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4908,33 +4908,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.079,00</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>▲ 44,7%</t>
+          <t>R$ 4.228,00</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>943</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▲ 9,1%</t>
+        <v>1001</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,4%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4990,11 +4990,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5054,33 +5054,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,7%</t>
+          <t>R$ 3.709,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,8%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>864</v>
+        <v>968</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>▼ 2,4%</t>
+          <t>▲ 5,8%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5138,9 +5138,9 @@
       <c r="I64" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5200,33 +5200,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.598,00</t>
+          <t>R$ 3.857,00</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>▼ 1,0%</t>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>885</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,4%</t>
+        <v>915</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5282,11 +5282,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5346,20 +5346,20 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.634,00</t>
+          <t>R$ 3.263,00</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>▲ 4,2%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1085</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▲ 8,4%</t>
+        <v>976</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,5%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5368,11 +5368,11 @@
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5389,12 +5389,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5428,11 +5428,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5492,33 +5492,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.486,00</t>
+          <t>R$ 4.079,00</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>▼ 22,9%</t>
+          <t>▲ 44,7%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1001</v>
+        <v>943</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>▼ 2,1%</t>
+          <t>▲ 9,1%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5574,11 +5574,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5638,33 +5638,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.524,00</t>
+          <t>R$ 2.818,00</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>▲ 1,7%</t>
+          <t>▼ 21,7%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1022</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▼ 1,7%</t>
+        <v>864</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,4%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5722,7 +5722,7 @@
       <c r="I72" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J72" s="4" t="inlineStr">
+      <c r="J72" s="3" t="inlineStr">
         <is>
           <t>▼ 75,0%</t>
         </is>
@@ -5754,12 +5754,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5784,33 +5784,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.450,00</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 3,2%</t>
+          <t>R$ 3.598,00</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 1,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1040</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 2,1%</t>
+        <v>885</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,4%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5930,33 +5930,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.599,00</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>▲ 21,4%</t>
+          <t>R$ 3.634,00</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1062</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▲ 12,9%</t>
+        <v>1085</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,4%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5973,12 +5973,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6012,11 +6012,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6046,12 +6046,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6076,33 +6076,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.787,00</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,7%</t>
+          <t>R$ 3.486,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,9%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>941</v>
+        <v>1001</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▲ 0,4%</t>
+          <t>▼ 2,1%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6119,12 +6119,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6158,11 +6158,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6192,12 +6192,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6222,20 +6222,20 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.239,00</t>
+          <t>R$ 4.524,00</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>▼ 5,7%</t>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>937</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>1022</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 1,7%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6244,11 +6244,11 @@
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6265,12 +6265,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6304,11 +6304,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6368,25 +6368,25 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.497,00</t>
+          <t>R$ 4.450,00</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,6%</t>
+          <t>▼ 3,2%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1006</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1040</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,1%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6450,11 +6450,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6514,33 +6514,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
+          <t>R$ 4.599,00</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,7%</t>
+          <t>▲ 21,4%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0</v>
+        <v>1062</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6596,11 +6596,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6630,12 +6630,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6660,33 +6660,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.192,00</t>
+          <t>R$ 3.787,00</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>▲ 32,1%</t>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>854</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▲ 0,7%</t>
+        <v>941</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,4%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6742,11 +6742,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6806,33 +6806,33 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
+          <t>R$ 4.239,00</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,2%</t>
+          <t>▼ 5,7%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>848</v>
+        <v>937</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>▲ 1,7%</t>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6882,17 +6882,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6952,33 +6952,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.115,00</t>
+          <t>R$ 4.497,00</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▲ 16,6%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>834</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,5%</t>
+        <v>1006</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6995,12 +6995,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7034,24 +7034,24 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7098,33 +7098,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.895,00</t>
+          <t>R$ 3.857,00</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,9%</t>
+          <t>▼ 25,7%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>976</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>▲ 8,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7180,11 +7180,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7244,33 +7244,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.857,00</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>▲ 36,9%</t>
+          <t>R$ 5.192,00</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,1%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>896</v>
+        <v>854</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>▼ 2,4%</t>
+          <t>▲ 0,7%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7326,11 +7326,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7360,12 +7360,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7390,33 +7390,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
+          <t>R$ 3.931,00</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,6%</t>
+          <t>▲ 26,2%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
+        <v>848</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
         <is>
           <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7433,12 +7433,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7466,17 +7466,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>2</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7536,20 +7536,20 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,1%</t>
+          <t>R$ 3.115,00</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>903</v>
+        <v>834</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,5%</t>
+          <t>▼ 14,5%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7558,11 +7558,11 @@
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7618,24 +7618,24 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7682,33 +7682,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.931,00</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>▲ 20,5%</t>
+          <t>R$ 4.895,00</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,9%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>817</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▲ 6,1%</t>
+        <v>976</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,9%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7725,12 +7725,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H100" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7798,12 +7798,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7828,33 +7828,33 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.263,00</t>
+          <t>R$ 3.857,00</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>▼ 34,3%</t>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>770</v>
-      </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,3%</t>
+        <v>896</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,4%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 73,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -7910,24 +7910,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -7974,33 +7974,33 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.969,00</t>
-        </is>
-      </c>
-      <c r="H103" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,9%</t>
+          <t>R$ 2.818,00</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>979</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▲ 0,6%</t>
+        <v>918</v>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,7%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8017,12 +8017,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8120,33 +8120,33 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.637,00</t>
+          <t>R$ 3.338,00</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>▲ 68,9%</t>
+          <t>▼ 15,1%</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>973</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>▲ 20,1%</t>
+        <v>903</v>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8202,11 +8202,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8236,12 +8236,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8266,33 +8266,33 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.338,00</t>
+          <t>R$ 3.931,00</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,1%</t>
+          <t>▲ 20,5%</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,4%</t>
+          <t>▲ 6,1%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8342,17 +8342,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8412,33 +8412,33 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.592,00</t>
+          <t>R$ 3.263,00</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>▲ 3,5%</t>
+          <t>▼ 34,3%</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>914</v>
-      </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,5%</t>
+        <v>770</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,3%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 73,00</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8494,24 +8494,24 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8558,33 +8558,33 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.472,00</t>
-        </is>
-      </c>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,3%</t>
+          <t>R$ 4.969,00</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>1057</v>
+        <v>979</v>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>▼ 1,7%</t>
+          <t>▲ 0,6%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8601,12 +8601,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8640,11 +8640,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8674,12 +8674,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8704,33 +8704,33 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.629,00</t>
+          <t>R$ 5.637,00</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,6%</t>
+          <t>▲ 68,9%</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1075</v>
+        <v>973</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>▼ 3,7%</t>
+          <t>▲ 20,1%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8786,11 +8786,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8850,20 +8850,20 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.747,00</t>
+          <t>R$ 3.338,00</t>
         </is>
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>▲ 68,5%</t>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>1116</v>
+        <v>810</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,7%</t>
+          <t>▼ 11,4%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8872,11 +8872,11 @@
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8926,17 +8926,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H116" s="4" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -8996,33 +8996,33 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.818,00</t>
+          <t>R$ 3.592,00</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>▼ 45,7%</t>
+          <t>▲ 3,5%</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>973</v>
-      </c>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>▼ 35,1%</t>
+        <v>914</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,5%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9039,12 +9039,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -9078,24 +9078,24 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K118" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9112,12 +9112,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9142,33 +9142,33 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.186,00</t>
+          <t>R$ 3.472,00</t>
         </is>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>▲ 45,7%</t>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>1500</v>
+        <v>1057</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>▲ 27,9%</t>
+          <t>▼ 1,7%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9224,11 +9224,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9258,12 +9258,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9288,33 +9288,33 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.560,00</t>
+          <t>R$ 3.629,00</t>
         </is>
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>▲ 4,3%</t>
+          <t>▼ 23,6%</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>1173</v>
-      </c>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>▼ 5,4%</t>
+        <v>1075</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,7%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -9331,12 +9331,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9370,11 +9370,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9434,33 +9434,33 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.412,00</t>
-        </is>
-      </c>
-      <c r="H123" s="3" t="inlineStr">
-        <is>
-          <t>▲ 17,9%</t>
+          <t>R$ 4.747,00</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>▲ 68,5%</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>▲ 6,4%</t>
+        <v>1116</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,7%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9510,17 +9510,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9550,12 +9550,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9580,33 +9580,33 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
-        </is>
-      </c>
-      <c r="H125" s="4" t="inlineStr">
-        <is>
-          <t>▼ 54,1%</t>
+          <t>R$ 2.818,00</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 45,7%</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>1165</v>
-      </c>
-      <c r="J125" s="4" t="inlineStr">
-        <is>
-          <t>▼ 47,2%</t>
+        <v>973</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,1%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9623,12 +9623,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -9662,24 +9662,24 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K126" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9696,12 +9696,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9726,33 +9726,33 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.304,00</t>
-        </is>
-      </c>
-      <c r="H127" s="3" t="inlineStr">
-        <is>
-          <t>▲ 117,9%</t>
+          <t>R$ 5.186,00</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t>▲ 45,7%</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>2206</v>
-      </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>▲ 101,1%</t>
+        <v>1500</v>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27,9%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -9808,11 +9808,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9842,12 +9842,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -9872,33 +9872,33 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.893,00</t>
-        </is>
-      </c>
-      <c r="H129" s="3" t="inlineStr">
-        <is>
-          <t>▲ 34,7%</t>
+          <t>R$ 3.560,00</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>1097</v>
+        <v>1173</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>▲ 18,0%</t>
+          <t>▼ 5,4%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -9988,12 +9988,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10018,33 +10018,33 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.147,00</t>
+          <t>R$ 3.412,00</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>930</v>
+        <v>1240</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,1%</t>
+          <t>▲ 6,4%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L131" s="2" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -10061,12 +10061,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       <c r="I132" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J132" s="4" t="inlineStr">
+      <c r="J132" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -10134,12 +10134,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10164,33 +10164,33 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.823,00</t>
-        </is>
-      </c>
-      <c r="H133" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,6%</t>
+          <t>R$ 2.893,00</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>▼ 54,1%</t>
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>1070</v>
+        <v>1165</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>▲ 0,8%</t>
+          <t>▼ 47,2%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L133" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10246,11 +10246,11 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J134" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10280,12 +10280,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10310,38 +10310,38 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.469,00</t>
+          <t>R$ 6.304,00</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,4%</t>
+          <t>▲ 117,9%</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>1061</v>
+        <v>2206</v>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>▼ 22,4%</t>
+          <t>▲ 101,1%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L135" s="2" t="n">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10392,11 +10392,11 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10456,33 +10456,33 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.708,00</t>
+          <t>R$ 2.893,00</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>▼ 0,9%</t>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>1368</v>
+        <v>1097</v>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,9%</t>
+          <t>▲ 18,0%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L137" s="2" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -10499,12 +10499,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10538,7 +10538,7 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -10572,12 +10572,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10602,33 +10602,33 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.742,00</t>
+          <t>R$ 2.147,00</t>
         </is>
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
-          <t>▲ 15,5%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>1485</v>
+        <v>930</v>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,6%</t>
+          <t>▼ 13,1%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L139" s="2" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
@@ -10645,12 +10645,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10686,9 +10686,9 @@
       <c r="I140" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10718,12 +10718,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10748,33 +10748,33 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.241,00</t>
-        </is>
-      </c>
-      <c r="H141" s="4" t="inlineStr">
-        <is>
-          <t>▼ 36,1%</t>
+          <t>R$ 2.823,00</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>1211</v>
-      </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>▲ 0,2%</t>
+        <v>1070</v>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L141" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -10830,11 +10830,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -10894,38 +10894,38 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.072,00</t>
+          <t>R$ 3.469,00</t>
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>▲ 9,1%</t>
+          <t>▼ 6,4%</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>1208</v>
-      </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>▼ 0,2%</t>
+        <v>1061</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,4%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L143" s="2" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O143" s="2" t="inlineStr">
@@ -10937,12 +10937,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -10976,11 +10976,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11010,12 +11010,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11040,33 +11040,33 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.650,00</t>
-        </is>
-      </c>
-      <c r="H145" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,4%</t>
+          <t>R$ 3.708,00</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,9%</t>
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>1211</v>
-      </c>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,6%</t>
+        <v>1368</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,9%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L145" s="2" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -11083,12 +11083,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11122,11 +11122,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11156,12 +11156,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11186,33 +11186,33 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.918,00</t>
-        </is>
-      </c>
-      <c r="H147" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,4%</t>
+          <t>R$ 3.742,00</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,5%</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>1402</v>
-      </c>
-      <c r="J147" s="3" t="inlineStr">
-        <is>
-          <t>▲ 0,3%</t>
+        <v>1485</v>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L147" s="2" t="n">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -11229,12 +11229,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11268,11 +11268,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11302,12 +11302,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11332,33 +11332,33 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.720,00</t>
-        </is>
-      </c>
-      <c r="H149" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,4%</t>
+          <t>R$ 3.241,00</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,1%</t>
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>1398</v>
+        <v>1211</v>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>▼ 9,3%</t>
+          <t>▲ 0,2%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L149" s="2" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -11375,12 +11375,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11414,11 +11414,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11448,12 +11448,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11478,33 +11478,33 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 6.246,00</t>
-        </is>
-      </c>
-      <c r="H151" s="3" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+          <t>R$ 5.072,00</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,1%</t>
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>1541</v>
+        <v>1208</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>▲ 23,9%</t>
+          <t>▼ 0,2%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L151" s="2" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -11521,12 +11521,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11560,11 +11560,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11594,12 +11594,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11624,33 +11624,33 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.677,00</t>
-        </is>
-      </c>
-      <c r="H153" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,0%</t>
+          <t>R$ 4.650,00</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>1244</v>
+        <v>1211</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>▲ 3,2%</t>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L153" s="2" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -11667,12 +11667,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11706,11 +11706,11 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -11770,38 +11770,38 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.523,00</t>
+          <t>R$ 5.918,00</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>▼ 19,3%</t>
+          <t>▲ 25,4%</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>1205</v>
+        <v>1402</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,3%</t>
+          <t>▲ 0,3%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L155" s="2" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -11846,17 +11846,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -11886,12 +11886,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -11916,33 +11916,33 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.368,00</t>
+          <t>R$ 4.720,00</t>
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>▲ 21,6%</t>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>1344</v>
+        <v>1398</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>▲ 1,9%</t>
+          <t>▼ 9,3%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -11959,12 +11959,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -11998,24 +11998,24 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12032,12 +12032,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12062,33 +12062,33 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.593,00</t>
+          <t>R$ 6.246,00</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>1319</v>
-      </c>
-      <c r="J159" s="3" t="inlineStr">
-        <is>
-          <t>▲ 0,8%</t>
+        <v>1541</v>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L159" s="2" t="n">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -12105,12 +12105,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12146,9 +12146,9 @@
       <c r="I160" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12208,33 +12208,33 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>R$ 4.791,00</t>
+          <t>R$ 2.677,00</t>
         </is>
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>▲ 30,8%</t>
+          <t>▼ 24,0%</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>1308</v>
+        <v>1244</v>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>▼ 1,4%</t>
+          <t>▲ 3,2%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L161" s="2" t="n">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
@@ -12251,12 +12251,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12290,11 +12290,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12324,12 +12324,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12354,33 +12354,33 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.663,00</t>
+          <t>R$ 3.523,00</t>
         </is>
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>▲ 23,8%</t>
+          <t>▼ 19,3%</t>
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>1326</v>
+        <v>1205</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>▲ 12,3%</t>
+          <t>▼ 10,3%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L163" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -12397,12 +12397,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12430,17 +12430,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12470,12 +12470,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12500,38 +12500,38 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.959,00</t>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 4.368,00</t>
+        </is>
+      </c>
+      <c r="H165" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>1181</v>
+        <v>1344</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,9%</t>
+          <t>▲ 1,9%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L165" s="2" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O165" s="2" t="inlineStr">
@@ -12543,12 +12543,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -12582,24 +12582,24 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K166" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L166" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12616,12 +12616,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12646,33 +12646,33 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 2.959,00</t>
-        </is>
-      </c>
-      <c r="H167" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+          <t>R$ 3.593,00</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>1268</v>
+        <v>1319</v>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>▼ 41,2%</t>
+          <t>▲ 0,8%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L167" s="2" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -12728,11 +12728,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12762,12 +12762,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -12792,33 +12792,33 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>R$ 5.988,00</t>
-        </is>
-      </c>
-      <c r="H169" s="3" t="inlineStr">
-        <is>
-          <t>▲ 94,0%</t>
+          <t>R$ 4.791,00</t>
+        </is>
+      </c>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>2156</v>
+        <v>1308</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>▲ 105,9%</t>
+          <t>▼ 1,4%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L169" s="2" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
@@ -12835,12 +12835,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -12876,9 +12876,9 @@
       <c r="I170" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J170" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -12938,38 +12938,38 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.086,00</t>
+          <t>R$ 3.663,00</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>▼ 2,6%</t>
+          <t>▲ 23,8%</t>
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>1047</v>
+        <v>1326</v>
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
-          <t>▼ 4,7%</t>
+          <t>▲ 12,3%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L171" s="2" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O171" s="2" t="inlineStr">
@@ -12981,12 +12981,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13020,11 +13020,11 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J172" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13054,12 +13054,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13084,38 +13084,38 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>R$ 3.170,00</t>
-        </is>
-      </c>
-      <c r="H173" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+          <t>R$ 2.959,00</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>1099</v>
-      </c>
-      <c r="J173" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,9%</t>
+        <v>1181</v>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L173" s="2" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O173" s="2" t="inlineStr">
@@ -13127,12 +13127,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13166,11 +13166,11 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J174" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
@@ -13200,78 +13200,662 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 2.959,00</t>
+        </is>
+      </c>
+      <c r="H175" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>1268</v>
+      </c>
+      <c r="J175" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,2%</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>34,4%</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 5.988,00</t>
+        </is>
+      </c>
+      <c r="H177" s="4" t="inlineStr">
+        <is>
+          <t>▲ 94,0%</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>2156</v>
+      </c>
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t>▲ 105,9%</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>56,8%</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J178" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.086,00</t>
+        </is>
+      </c>
+      <c r="H179" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>1047</v>
+      </c>
+      <c r="J179" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,7%</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>40,2%</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>3284176106</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.170,00</t>
+        </is>
+      </c>
+      <c r="H181" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="J181" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>UTD-092</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo Inox</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>6420379554</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-092</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo Inox</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>3284176106</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>R$ 4.227,00</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I175" s="2" t="n">
+      <c r="I183" s="2" t="n">
         <v>1247</v>
       </c>
-      <c r="J175" s="2" t="inlineStr">
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K175" s="2" t="inlineStr">
+      <c r="K183" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="L175" s="2" t="n">
+      <c r="L183" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="M175" s="2" t="inlineStr">
+      <c r="M183" s="2" t="inlineStr">
         <is>
           <t>45,9%</t>
         </is>
       </c>
-      <c r="N175" s="2" t="inlineStr">
+      <c r="N183" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>